--- a/research/traditional_assets/database/data/netherlands/netherlands_retail_distributors.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_retail_distributors.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07085377930559372</v>
+        <v>0.0707043665549853</v>
       </c>
       <c r="C2">
-        <v>9674.714839230006</v>
+        <v>9624.035127876818</v>
       </c>
       <c r="D2">
-        <v>9434.914839230007</v>
+        <v>9491.519233273644</v>
       </c>
       <c r="E2">
-        <v>-1952.710539682522</v>
+        <v>-1845.426434285696</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>107.2841053968252</v>
       </c>
       <c r="G2">
         <v>239.8</v>
@@ -1457,28 +1457,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.396390501460308</v>
       </c>
       <c r="N2">
-        <v>415.4099999999999</v>
+        <v>410.0136094985396</v>
       </c>
       <c r="O2">
-        <v>107.17578</v>
+        <v>105.7835112506232</v>
       </c>
       <c r="P2">
-        <v>308.2342199999999</v>
+        <v>304.2300982479164</v>
       </c>
       <c r="Q2">
-        <v>444.5342199999999</v>
+        <v>440.5300982479164</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07085377930559372</v>
+        <v>0.07104155611614676</v>
       </c>
       <c r="T2">
-        <v>0.5786092218381922</v>
+        <v>0.5829458687331814</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>76.9792326718362</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0707043665549853</v>
+        <v>0.07055495380437685</v>
       </c>
       <c r="C3">
-        <v>9624.035127876818</v>
+        <v>9574.038707494607</v>
       </c>
       <c r="D3">
-        <v>9491.519233273644</v>
+        <v>9548.806918288257</v>
       </c>
       <c r="E3">
-        <v>-1845.426434285696</v>
+        <v>-1738.142328888871</v>
       </c>
       <c r="F3">
-        <v>107.2841053968252</v>
+        <v>214.5682107936505</v>
       </c>
       <c r="G3">
         <v>239.8</v>
@@ -1539,28 +1539,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M3">
-        <v>5.396390501460308</v>
+        <v>10.79278100292062</v>
       </c>
       <c r="N3">
-        <v>410.0136094985396</v>
+        <v>404.6172189970793</v>
       </c>
       <c r="O3">
-        <v>105.7835112506232</v>
+        <v>104.3912425012465</v>
       </c>
       <c r="P3">
-        <v>304.2300982479164</v>
+        <v>300.2259764958328</v>
       </c>
       <c r="Q3">
-        <v>440.5300982479164</v>
+        <v>436.5259764958328</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07104155611614676</v>
+        <v>0.071233165106507</v>
       </c>
       <c r="T3">
-        <v>0.5829458687331814</v>
+        <v>0.5873710186260277</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>76.9792326718362</v>
+        <v>38.4896163359181</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07055495380437685</v>
+        <v>0.07040554105376842</v>
       </c>
       <c r="C4">
-        <v>9574.038707494607</v>
+        <v>9524.738025570263</v>
       </c>
       <c r="D4">
-        <v>9548.806918288257</v>
+        <v>9606.790341760739</v>
       </c>
       <c r="E4">
-        <v>-1738.142328888871</v>
+        <v>-1630.858223492046</v>
       </c>
       <c r="F4">
-        <v>214.5682107936505</v>
+        <v>321.8523161904756</v>
       </c>
       <c r="G4">
         <v>239.8</v>
@@ -1621,28 +1621,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M4">
-        <v>10.79278100292062</v>
+        <v>16.18917150438092</v>
       </c>
       <c r="N4">
-        <v>404.6172189970793</v>
+        <v>399.220828495619</v>
       </c>
       <c r="O4">
-        <v>104.3912425012465</v>
+        <v>102.9989737518697</v>
       </c>
       <c r="P4">
-        <v>300.2259764958328</v>
+        <v>296.2218547437493</v>
       </c>
       <c r="Q4">
-        <v>436.5259764958328</v>
+        <v>432.5218547437493</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.071233165106507</v>
+        <v>0.07142872479769941</v>
       </c>
       <c r="T4">
-        <v>0.5873710186260277</v>
+        <v>0.5918874087228501</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>38.4896163359181</v>
+        <v>25.65974422394541</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07040554105376842</v>
+        <v>0.07025612830316001</v>
       </c>
       <c r="C5">
-        <v>9524.738025570263</v>
+        <v>9476.145833778395</v>
       </c>
       <c r="D5">
-        <v>9606.790341760739</v>
+        <v>9665.482255365696</v>
       </c>
       <c r="E5">
-        <v>-1630.858223492046</v>
+        <v>-1523.574118095221</v>
       </c>
       <c r="F5">
-        <v>321.8523161904756</v>
+        <v>429.1364215873009</v>
       </c>
       <c r="G5">
         <v>239.8</v>
@@ -1703,28 +1703,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M5">
-        <v>16.18917150438092</v>
+        <v>21.58556200584123</v>
       </c>
       <c r="N5">
-        <v>399.220828495619</v>
+        <v>393.8244379941587</v>
       </c>
       <c r="O5">
-        <v>102.9989737518697</v>
+        <v>101.6067050024929</v>
       </c>
       <c r="P5">
-        <v>296.2218547437493</v>
+        <v>292.2177329916657</v>
       </c>
       <c r="Q5">
-        <v>432.5218547437493</v>
+        <v>428.5177329916658</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07142872479769941</v>
+        <v>0.07162835864912501</v>
       </c>
       <c r="T5">
-        <v>0.5918874087228501</v>
+        <v>0.596497890280023</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>25.65974422394541</v>
+        <v>19.24480816795905</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07025612830316001</v>
+        <v>0.07010671555255157</v>
       </c>
       <c r="C6">
-        <v>9476.145833778395</v>
+        <v>9428.275197330468</v>
       </c>
       <c r="D6">
-        <v>9665.482255365696</v>
+        <v>9724.895724314594</v>
       </c>
       <c r="E6">
-        <v>-1523.574118095221</v>
+        <v>-1416.290012698395</v>
       </c>
       <c r="F6">
-        <v>429.1364215873009</v>
+        <v>536.4205269841261</v>
       </c>
       <c r="G6">
         <v>239.8</v>
@@ -1785,28 +1785,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M6">
-        <v>21.58556200584123</v>
+        <v>26.98195250730154</v>
       </c>
       <c r="N6">
-        <v>393.8244379941587</v>
+        <v>388.4280474926984</v>
       </c>
       <c r="O6">
-        <v>101.6067050024929</v>
+        <v>100.2144362531162</v>
       </c>
       <c r="P6">
-        <v>292.2177329916657</v>
+        <v>288.2136112395822</v>
       </c>
       <c r="Q6">
-        <v>428.5177329916658</v>
+        <v>424.5136112395822</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07162835864912501</v>
+        <v>0.07183219531847534</v>
       </c>
       <c r="T6">
-        <v>0.596497890280023</v>
+        <v>0.6012054346068206</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>19.24480816795905</v>
+        <v>15.39584653436724</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07010671555255157</v>
+        <v>0.06995730280194312</v>
       </c>
       <c r="C7">
-        <v>9428.275197330468</v>
+        <v>9381.1395046709</v>
       </c>
       <c r="D7">
-        <v>9724.895724314594</v>
+        <v>9785.044137051853</v>
       </c>
       <c r="E7">
-        <v>-1416.290012698395</v>
+        <v>-1309.00590730157</v>
       </c>
       <c r="F7">
-        <v>536.4205269841261</v>
+        <v>643.7046323809514</v>
       </c>
       <c r="G7">
         <v>239.8</v>
@@ -1867,28 +1867,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M7">
-        <v>26.98195250730154</v>
+        <v>32.37834300876185</v>
       </c>
       <c r="N7">
-        <v>388.4280474926984</v>
+        <v>383.031656991238</v>
       </c>
       <c r="O7">
-        <v>100.2144362531162</v>
+        <v>98.82216750373942</v>
       </c>
       <c r="P7">
-        <v>288.2136112395822</v>
+        <v>284.2094894874986</v>
       </c>
       <c r="Q7">
-        <v>424.5136112395822</v>
+        <v>420.5094894874986</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07183219531847534</v>
+        <v>0.07204036893823737</v>
       </c>
       <c r="T7">
-        <v>0.6012054346068206</v>
+        <v>0.6060131394512095</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>15.39584653436724</v>
+        <v>12.8298721119727</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.06995730280194312</v>
+        <v>0.06980789005133471</v>
       </c>
       <c r="C8">
-        <v>9381.1395046709</v>
+        <v>9334.752477535243</v>
       </c>
       <c r="D8">
-        <v>9785.044137051853</v>
+        <v>9845.94121531302</v>
       </c>
       <c r="E8">
-        <v>-1309.00590730157</v>
+        <v>-1201.721801904745</v>
       </c>
       <c r="F8">
-        <v>643.7046323809512</v>
+        <v>750.9887377777765</v>
       </c>
       <c r="G8">
         <v>239.8</v>
@@ -1949,28 +1949,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M8">
-        <v>32.37834300876185</v>
+        <v>37.77473351022216</v>
       </c>
       <c r="N8">
-        <v>383.031656991238</v>
+        <v>377.6352664897777</v>
       </c>
       <c r="O8">
-        <v>98.82216750373942</v>
+        <v>97.42989875436265</v>
       </c>
       <c r="P8">
-        <v>284.2094894874986</v>
+        <v>280.2053677354151</v>
       </c>
       <c r="Q8">
-        <v>420.5094894874986</v>
+        <v>416.5053677354151</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07204036893823737</v>
+        <v>0.07225301941003731</v>
       </c>
       <c r="T8">
-        <v>0.6060131394512095</v>
+        <v>0.6109242357976284</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>12.8298721119727</v>
+        <v>10.99703323883374</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0698078900513347</v>
+        <v>0.06965847730072627</v>
       </c>
       <c r="C9">
-        <v>9334.752477535249</v>
+        <v>9289.12818138635</v>
       </c>
       <c r="D9">
-        <v>9845.941215313025</v>
+        <v>9907.601024560952</v>
       </c>
       <c r="E9">
-        <v>-1201.721801904745</v>
+        <v>-1094.43769650792</v>
       </c>
       <c r="F9">
-        <v>750.9887377777766</v>
+        <v>858.2728431746018</v>
       </c>
       <c r="G9">
         <v>239.8</v>
@@ -2031,28 +2031,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M9">
-        <v>37.77473351022216</v>
+        <v>43.17112401168247</v>
       </c>
       <c r="N9">
-        <v>377.6352664897777</v>
+        <v>372.2388759883174</v>
       </c>
       <c r="O9">
-        <v>97.42989875436265</v>
+        <v>96.0376300049859</v>
       </c>
       <c r="P9">
-        <v>280.2053677354151</v>
+        <v>276.2012459833315</v>
       </c>
       <c r="Q9">
-        <v>416.5053677354151</v>
+        <v>412.5012459833316</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07225301941003731</v>
+        <v>0.07247029271818073</v>
       </c>
       <c r="T9">
-        <v>0.6109242357976284</v>
+        <v>0.6159420951080998</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>10.99703323883374</v>
+        <v>9.622404083979525</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.06965847730072627</v>
+        <v>0.06960923455011783</v>
       </c>
       <c r="C10">
-        <v>9289.12818138635</v>
+        <v>9202.335181041784</v>
       </c>
       <c r="D10">
-        <v>9907.601024560952</v>
+        <v>9928.092129613213</v>
       </c>
       <c r="E10">
-        <v>-1094.43769650792</v>
+        <v>-987.1535911110947</v>
       </c>
       <c r="F10">
-        <v>858.2728431746018</v>
+        <v>965.5569485714269</v>
       </c>
       <c r="G10">
         <v>239.8</v>
@@ -2113,45 +2113,45 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M10">
-        <v>43.17112401168247</v>
+        <v>50.01584993599991</v>
       </c>
       <c r="N10">
-        <v>372.2388759883174</v>
+        <v>365.394150064</v>
       </c>
       <c r="O10">
-        <v>96.0376300049859</v>
+        <v>94.271690716512</v>
       </c>
       <c r="P10">
-        <v>276.2012459833315</v>
+        <v>271.122459347488</v>
       </c>
       <c r="Q10">
-        <v>412.5012459833316</v>
+        <v>407.422459347488</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07247029271818073</v>
+        <v>0.07269234126386576</v>
       </c>
       <c r="T10">
-        <v>0.6159420951080998</v>
+        <v>0.6210702370407796</v>
       </c>
       <c r="U10">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y10">
-        <v>9.622404083979525</v>
+        <v>8.305567145845906</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.06960923455011783</v>
+        <v>0.06947095179950941</v>
       </c>
       <c r="C11">
-        <v>9202.335181041784</v>
+        <v>9153.049752656556</v>
       </c>
       <c r="D11">
-        <v>9928.092129613213</v>
+        <v>9986.090806624808</v>
       </c>
       <c r="E11">
-        <v>-987.1535911110947</v>
+        <v>-879.8694857142696</v>
       </c>
       <c r="F11">
-        <v>965.5569485714269</v>
+        <v>1072.841053968252</v>
       </c>
       <c r="G11">
         <v>239.8</v>
@@ -2195,28 +2195,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M11">
-        <v>50.01584993599991</v>
+        <v>55.57316659555546</v>
       </c>
       <c r="N11">
-        <v>365.394150064</v>
+        <v>359.8368334044445</v>
       </c>
       <c r="O11">
-        <v>94.271690716512</v>
+        <v>92.83790301834668</v>
       </c>
       <c r="P11">
-        <v>271.122459347488</v>
+        <v>266.9989303860978</v>
       </c>
       <c r="Q11">
-        <v>407.422459347488</v>
+        <v>403.2989303860978</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07269234126386576</v>
+        <v>0.07291932422167711</v>
       </c>
       <c r="T11">
-        <v>0.6210702370407796</v>
+        <v>0.6263123376830743</v>
       </c>
       <c r="U11">
         <v>0.0518</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.305567145845906</v>
+        <v>7.475010431261316</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.06947095179950941</v>
+        <v>0.06933266904890098</v>
       </c>
       <c r="C12">
-        <v>9153.049752656556</v>
+        <v>9104.445948321036</v>
       </c>
       <c r="D12">
-        <v>9986.090806624808</v>
+        <v>10044.77110768611</v>
       </c>
       <c r="E12">
-        <v>-879.8694857142693</v>
+        <v>-772.5853803174441</v>
       </c>
       <c r="F12">
-        <v>1072.841053968252</v>
+        <v>1180.125159365077</v>
       </c>
       <c r="G12">
         <v>239.8</v>
@@ -2277,28 +2277,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M12">
-        <v>55.57316659555546</v>
+        <v>61.13048325511101</v>
       </c>
       <c r="N12">
-        <v>359.8368334044445</v>
+        <v>354.2795167448889</v>
       </c>
       <c r="O12">
-        <v>92.83790301834668</v>
+        <v>91.40411532018133</v>
       </c>
       <c r="P12">
-        <v>266.9989303860978</v>
+        <v>262.8754014247075</v>
       </c>
       <c r="Q12">
-        <v>403.2989303860978</v>
+        <v>399.1754014247076</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07291932422167711</v>
+        <v>0.07315140792011346</v>
       </c>
       <c r="T12">
-        <v>0.6263123376830743</v>
+        <v>0.6316722383398026</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>7.475010431261315</v>
+        <v>6.795464028419376</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.06933266904890098</v>
+        <v>0.06934575429829254</v>
       </c>
       <c r="C13">
-        <v>9104.445948321036</v>
+        <v>8991.579590881654</v>
       </c>
       <c r="D13">
-        <v>10044.77110768611</v>
+        <v>10039.18885564356</v>
       </c>
       <c r="E13">
-        <v>-772.5853803174441</v>
+        <v>-665.3012749206191</v>
       </c>
       <c r="F13">
-        <v>1180.125159365077</v>
+        <v>1287.409264761902</v>
       </c>
       <c r="G13">
         <v>239.8</v>
@@ -2359,45 +2359,45 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M13">
-        <v>61.13048325511101</v>
+        <v>68.87639566476179</v>
       </c>
       <c r="N13">
-        <v>354.2795167448889</v>
+        <v>346.5336043352381</v>
       </c>
       <c r="O13">
-        <v>91.40411532018133</v>
+        <v>89.40566991849144</v>
       </c>
       <c r="P13">
-        <v>262.8754014247075</v>
+        <v>257.1279344167467</v>
       </c>
       <c r="Q13">
-        <v>399.1754014247076</v>
+        <v>393.4279344167467</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07315140792011346</v>
+        <v>0.07338876624805971</v>
       </c>
       <c r="T13">
-        <v>0.6316722383398026</v>
+        <v>0.6371539549205475</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>6.795464028419376</v>
+        <v>6.031238946095578</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.06934575429829254</v>
+        <v>0.06929725354768411</v>
       </c>
       <c r="C14">
-        <v>8991.579590881654</v>
+        <v>8905.017404921515</v>
       </c>
       <c r="D14">
-        <v>10039.18885564356</v>
+        <v>10059.91077508024</v>
       </c>
       <c r="E14">
-        <v>-665.3012749206191</v>
+        <v>-558.0171695237937</v>
       </c>
       <c r="F14">
-        <v>1287.409264761902</v>
+        <v>1394.693370158728</v>
       </c>
       <c r="G14">
         <v>239.8</v>
@@ -2441,45 +2441,45 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M14">
-        <v>68.87639566476179</v>
+        <v>75.73184999961893</v>
       </c>
       <c r="N14">
-        <v>346.5336043352381</v>
+        <v>339.678150000381</v>
       </c>
       <c r="O14">
-        <v>89.40566991849144</v>
+        <v>87.63696270009829</v>
       </c>
       <c r="P14">
-        <v>257.1279344167467</v>
+        <v>252.0411873002827</v>
       </c>
       <c r="Q14">
-        <v>393.4279344167467</v>
+        <v>388.3411873002827</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07338876624805971</v>
+        <v>0.07363158108929208</v>
       </c>
       <c r="T14">
-        <v>0.6371539549205475</v>
+        <v>0.6427616879744129</v>
       </c>
       <c r="U14">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y14">
-        <v>6.031238946095578</v>
+        <v>5.485274689606687</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.06929725354768411</v>
+        <v>0.06917752079707569</v>
       </c>
       <c r="C15">
-        <v>8905.017404921515</v>
+        <v>8849.257188581663</v>
       </c>
       <c r="D15">
-        <v>10059.91077508024</v>
+        <v>10111.43466413722</v>
       </c>
       <c r="E15">
-        <v>-558.0171695237937</v>
+        <v>-450.7330641269684</v>
       </c>
       <c r="F15">
-        <v>1394.693370158728</v>
+        <v>1501.977475555553</v>
       </c>
       <c r="G15">
         <v>239.8</v>
@@ -2523,28 +2523,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M15">
-        <v>75.73184999961893</v>
+        <v>81.55737692266653</v>
       </c>
       <c r="N15">
-        <v>339.678150000381</v>
+        <v>333.8526230773334</v>
       </c>
       <c r="O15">
-        <v>87.63696270009829</v>
+        <v>86.13397675395201</v>
       </c>
       <c r="P15">
-        <v>252.0411873002827</v>
+        <v>247.7186463233813</v>
       </c>
       <c r="Q15">
-        <v>388.3411873002827</v>
+        <v>384.0186463233813</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07363158108929208</v>
+        <v>0.0738800427872973</v>
       </c>
       <c r="T15">
-        <v>0.6427616879744129</v>
+        <v>0.6484998334248799</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>5.485274689606687</v>
+        <v>5.093469354634781</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.06917752079707569</v>
+        <v>0.06905778804646726</v>
       </c>
       <c r="C16">
-        <v>8849.257188581663</v>
+        <v>8794.027469548486</v>
       </c>
       <c r="D16">
-        <v>10111.43466413722</v>
+        <v>10163.48905050086</v>
       </c>
       <c r="E16">
-        <v>-450.7330641269684</v>
+        <v>-343.4489587301432</v>
       </c>
       <c r="F16">
-        <v>1501.977475555553</v>
+        <v>1609.261580952378</v>
       </c>
       <c r="G16">
         <v>239.8</v>
@@ -2605,28 +2605,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M16">
-        <v>81.55737692266653</v>
+        <v>87.38290384571415</v>
       </c>
       <c r="N16">
-        <v>333.8526230773334</v>
+        <v>328.0270961542857</v>
       </c>
       <c r="O16">
-        <v>86.13397675395201</v>
+        <v>84.63099080780573</v>
       </c>
       <c r="P16">
-        <v>247.7186463233813</v>
+        <v>243.39610534648</v>
       </c>
       <c r="Q16">
-        <v>384.0186463233813</v>
+        <v>379.69610534648</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.0738800427872973</v>
+        <v>0.07413435064290265</v>
       </c>
       <c r="T16">
-        <v>0.6484998334248799</v>
+        <v>0.6543729940624167</v>
       </c>
       <c r="U16">
         <v>0.0543</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.093469354634781</v>
+        <v>4.753904730992462</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.06905778804646726</v>
+        <v>0.06893805529585881</v>
       </c>
       <c r="C17">
-        <v>8794.027469548486</v>
+        <v>8739.336483332818</v>
       </c>
       <c r="D17">
-        <v>10163.48905050086</v>
+        <v>10216.08216968202</v>
       </c>
       <c r="E17">
-        <v>-343.4489587301434</v>
+        <v>-236.164853333318</v>
       </c>
       <c r="F17">
-        <v>1609.261580952378</v>
+        <v>1716.545686349204</v>
       </c>
       <c r="G17">
         <v>239.8</v>
@@ -2687,28 +2687,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M17">
-        <v>87.38290384571414</v>
+        <v>93.20843076876176</v>
       </c>
       <c r="N17">
-        <v>328.0270961542858</v>
+        <v>322.2015692312382</v>
       </c>
       <c r="O17">
-        <v>84.63099080780574</v>
+        <v>83.12800486165945</v>
       </c>
       <c r="P17">
-        <v>243.3961053464801</v>
+        <v>239.0735643695787</v>
       </c>
       <c r="Q17">
-        <v>379.6961053464801</v>
+        <v>375.3735643695787</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07413435064290265</v>
+        <v>0.07439471344745097</v>
       </c>
       <c r="T17">
-        <v>0.6543729940624167</v>
+        <v>0.66038599185799</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>4.753904730992463</v>
+        <v>4.456785685305434</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.06893805529585881</v>
+        <v>0.06894446254525038</v>
       </c>
       <c r="C18">
-        <v>8739.336483332818</v>
+        <v>8629.224185830082</v>
       </c>
       <c r="D18">
-        <v>10216.08216968202</v>
+        <v>10213.25397757611</v>
       </c>
       <c r="E18">
-        <v>-236.164853333318</v>
+        <v>-128.8807479364928</v>
       </c>
       <c r="F18">
-        <v>1716.545686349204</v>
+        <v>1823.829791746029</v>
       </c>
       <c r="G18">
         <v>239.8</v>
@@ -2769,45 +2769,45 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M18">
-        <v>93.20843076876176</v>
+        <v>100.8577874835554</v>
       </c>
       <c r="N18">
-        <v>322.2015692312382</v>
+        <v>314.5522125164445</v>
       </c>
       <c r="O18">
-        <v>83.12800486165945</v>
+        <v>81.15447082924268</v>
       </c>
       <c r="P18">
-        <v>239.0735643695787</v>
+        <v>233.3977416872018</v>
       </c>
       <c r="Q18">
-        <v>375.3735643695787</v>
+        <v>369.6977416872019</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07439471344745097</v>
+        <v>0.07466135005451854</v>
       </c>
       <c r="T18">
-        <v>0.66038599185799</v>
+        <v>0.6665438811667098</v>
       </c>
       <c r="U18">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0402906</v>
+        <v>0.0410326</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>4.456785685305434</v>
+        <v>4.118769708960068</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06894446254525038</v>
+        <v>0.06883214979464194</v>
       </c>
       <c r="C19">
-        <v>8629.224185830082</v>
+        <v>8571.743449077161</v>
       </c>
       <c r="D19">
-        <v>10213.25397757611</v>
+        <v>10263.05734622002</v>
       </c>
       <c r="E19">
-        <v>-128.8807479364928</v>
+        <v>-21.59664253966753</v>
       </c>
       <c r="F19">
-        <v>1823.829791746029</v>
+        <v>1931.113897142854</v>
       </c>
       <c r="G19">
         <v>239.8</v>
@@ -2851,28 +2851,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M19">
-        <v>100.8577874835554</v>
+        <v>106.7905985119998</v>
       </c>
       <c r="N19">
-        <v>314.5522125164445</v>
+        <v>308.6194014880001</v>
       </c>
       <c r="O19">
-        <v>81.15447082924268</v>
+        <v>79.62380558390403</v>
       </c>
       <c r="P19">
-        <v>233.3977416872018</v>
+        <v>228.9955959040961</v>
       </c>
       <c r="Q19">
-        <v>369.6977416872019</v>
+        <v>365.2955959040961</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07466135005451854</v>
+        <v>0.07493448999346579</v>
       </c>
       <c r="T19">
-        <v>0.6665438811667098</v>
+        <v>0.6728519628975933</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>4.118769708960068</v>
+        <v>3.889949169573399</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06883214979464196</v>
+        <v>0.06871983704403352</v>
       </c>
       <c r="C20">
-        <v>8571.743449077156</v>
+        <v>8514.750809452604</v>
       </c>
       <c r="D20">
-        <v>10263.05734622001</v>
+        <v>10313.34881199228</v>
       </c>
       <c r="E20">
-        <v>-21.59664253966776</v>
+        <v>85.68746285715747</v>
       </c>
       <c r="F20">
-        <v>1931.113897142854</v>
+        <v>2038.398002539679</v>
       </c>
       <c r="G20">
         <v>239.8</v>
@@ -2933,28 +2933,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M20">
-        <v>106.7905985119998</v>
+        <v>112.7234095404443</v>
       </c>
       <c r="N20">
-        <v>308.6194014880001</v>
+        <v>302.6865904595556</v>
       </c>
       <c r="O20">
-        <v>79.62380558390403</v>
+        <v>78.09314033856536</v>
       </c>
       <c r="P20">
-        <v>228.9955959040961</v>
+        <v>224.5934501209903</v>
       </c>
       <c r="Q20">
-        <v>365.2955959040961</v>
+        <v>360.8934501209903</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07493448999346579</v>
+        <v>0.07521437412843644</v>
       </c>
       <c r="T20">
-        <v>0.6728519628975933</v>
+        <v>0.6793157997329432</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>3.889949169573399</v>
+        <v>3.685215002753746</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06871983704403352</v>
+        <v>0.06860752429342509</v>
       </c>
       <c r="C21">
-        <v>8514.750809452604</v>
+        <v>8458.253477672981</v>
       </c>
       <c r="D21">
-        <v>10313.34881199228</v>
+        <v>10364.13558560949</v>
       </c>
       <c r="E21">
-        <v>85.68746285715747</v>
+        <v>192.9715682539829</v>
       </c>
       <c r="F21">
-        <v>2038.398002539679</v>
+        <v>2145.682107936505</v>
       </c>
       <c r="G21">
         <v>239.8</v>
@@ -3015,28 +3015,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M21">
-        <v>112.7234095404443</v>
+        <v>118.6562205688887</v>
       </c>
       <c r="N21">
-        <v>302.6865904595556</v>
+        <v>296.7537794311112</v>
       </c>
       <c r="O21">
-        <v>78.09314033856536</v>
+        <v>76.56247509322668</v>
       </c>
       <c r="P21">
-        <v>224.5934501209903</v>
+        <v>220.1913043378845</v>
       </c>
       <c r="Q21">
-        <v>360.8934501209903</v>
+        <v>356.4913043378845</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07521437412843644</v>
+        <v>0.07550125536678136</v>
       </c>
       <c r="T21">
-        <v>0.6793157997329432</v>
+        <v>0.6859412324891768</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.685215002753746</v>
+        <v>3.500954252616058</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06860752429342509</v>
+        <v>0.06849521154281667</v>
       </c>
       <c r="C22">
-        <v>8458.253477672981</v>
+        <v>8402.258807190759</v>
       </c>
       <c r="D22">
-        <v>10364.13558560949</v>
+        <v>10415.42502052409</v>
       </c>
       <c r="E22">
-        <v>192.9715682539829</v>
+        <v>300.2556736508084</v>
       </c>
       <c r="F22">
-        <v>2145.682107936505</v>
+        <v>2252.96621333333</v>
       </c>
       <c r="G22">
         <v>239.8</v>
@@ -3097,28 +3097,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M22">
-        <v>118.6562205688887</v>
+        <v>124.5890315973331</v>
       </c>
       <c r="N22">
-        <v>296.7537794311112</v>
+        <v>290.8209684026668</v>
       </c>
       <c r="O22">
-        <v>76.56247509322668</v>
+        <v>75.03180984788803</v>
       </c>
       <c r="P22">
-        <v>220.1913043378845</v>
+        <v>215.7891585547787</v>
       </c>
       <c r="Q22">
-        <v>356.4913043378845</v>
+        <v>352.0891585547787</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07550125536678136</v>
+        <v>0.07579539942128691</v>
       </c>
       <c r="T22">
-        <v>0.6859412324891768</v>
+        <v>0.6927343977202519</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>3.500954252616058</v>
+        <v>3.334242145348627</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06849521154281667</v>
+        <v>0.06838289879220821</v>
       </c>
       <c r="C23">
-        <v>8402.258807190759</v>
+        <v>8346.774297743714</v>
       </c>
       <c r="D23">
-        <v>10415.42502052409</v>
+        <v>10467.22461647387</v>
       </c>
       <c r="E23">
-        <v>300.2556736508079</v>
+        <v>407.5397790476334</v>
       </c>
       <c r="F23">
-        <v>2252.96621333333</v>
+        <v>2360.250318730155</v>
       </c>
       <c r="G23">
         <v>239.8</v>
@@ -3179,28 +3179,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M23">
-        <v>124.5890315973331</v>
+        <v>130.5218426257776</v>
       </c>
       <c r="N23">
-        <v>290.8209684026668</v>
+        <v>284.8881573742224</v>
       </c>
       <c r="O23">
-        <v>75.03180984788803</v>
+        <v>73.50114460254937</v>
       </c>
       <c r="P23">
-        <v>215.7891585547787</v>
+        <v>211.387012771673</v>
       </c>
       <c r="Q23">
-        <v>352.0891585547787</v>
+        <v>347.687012771673</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07579539942128691</v>
+        <v>0.07609708563103618</v>
       </c>
       <c r="T23">
-        <v>0.6927343977202518</v>
+        <v>0.6997017466752005</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.334242145348627</v>
+        <v>3.182685684196417</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06838289879220821</v>
+        <v>0.0682705860415998</v>
       </c>
       <c r="C24">
-        <v>8346.774297743714</v>
+        <v>8291.80759901069</v>
       </c>
       <c r="D24">
-        <v>10467.22461647387</v>
+        <v>10519.54202313767</v>
       </c>
       <c r="E24">
-        <v>407.5397790476334</v>
+        <v>514.8238844444584</v>
       </c>
       <c r="F24">
-        <v>2360.250318730155</v>
+        <v>2467.53442412698</v>
       </c>
       <c r="G24">
         <v>239.8</v>
@@ -3261,28 +3261,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M24">
-        <v>130.5218426257776</v>
+        <v>136.454653654222</v>
       </c>
       <c r="N24">
-        <v>284.8881573742224</v>
+        <v>278.9553463457779</v>
       </c>
       <c r="O24">
-        <v>73.50114460254937</v>
+        <v>71.97047935721071</v>
       </c>
       <c r="P24">
-        <v>211.387012771673</v>
+        <v>206.9848669885672</v>
       </c>
       <c r="Q24">
-        <v>347.687012771673</v>
+        <v>343.2848669885672</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07609708563103618</v>
+        <v>0.0764066078462335</v>
       </c>
       <c r="T24">
-        <v>0.6997017466752005</v>
+        <v>0.7068500657328751</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>3.182685684196417</v>
+        <v>3.044308045753094</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.0682705860415998</v>
+        <v>0.06860347329099137</v>
       </c>
       <c r="C25">
-        <v>8291.80759901069</v>
+        <v>8030.958229048456</v>
       </c>
       <c r="D25">
-        <v>10519.54202313767</v>
+        <v>10365.97675857226</v>
       </c>
       <c r="E25">
-        <v>514.8238844444584</v>
+        <v>622.1079898412838</v>
       </c>
       <c r="F25">
-        <v>2467.53442412698</v>
+        <v>2574.818529523805</v>
       </c>
       <c r="G25">
         <v>239.8</v>
@@ -3343,45 +3343,45 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M25">
-        <v>136.454653654222</v>
+        <v>148.824511006476</v>
       </c>
       <c r="N25">
-        <v>278.9553463457779</v>
+        <v>266.5854889935239</v>
       </c>
       <c r="O25">
-        <v>71.97047935721071</v>
+        <v>68.77905616032918</v>
       </c>
       <c r="P25">
-        <v>206.9848669885672</v>
+        <v>197.8064328331948</v>
       </c>
       <c r="Q25">
-        <v>343.2848669885672</v>
+        <v>334.1064328331948</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0764066078462335</v>
+        <v>0.07672427538288337</v>
       </c>
       <c r="T25">
-        <v>0.7068500657328751</v>
+        <v>0.7141864984499623</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.0410326</v>
+        <v>0.0428876</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>3.044308045753094</v>
+        <v>2.791274079724164</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06860347329099137</v>
+        <v>0.06850971054038293</v>
       </c>
       <c r="C26">
-        <v>8030.958229048456</v>
+        <v>7966.472665354683</v>
       </c>
       <c r="D26">
-        <v>10365.97675857226</v>
+        <v>10408.77530027531</v>
       </c>
       <c r="E26">
-        <v>622.1079898412834</v>
+        <v>729.3920952381088</v>
       </c>
       <c r="F26">
-        <v>2574.818529523805</v>
+        <v>2682.10263492063</v>
       </c>
       <c r="G26">
         <v>239.8</v>
@@ -3425,28 +3425,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M26">
-        <v>148.8245110064759</v>
+        <v>155.0255322984125</v>
       </c>
       <c r="N26">
-        <v>266.585488993524</v>
+        <v>260.3844677015875</v>
       </c>
       <c r="O26">
-        <v>68.77905616032919</v>
+        <v>67.17919266700957</v>
       </c>
       <c r="P26">
-        <v>197.8064328331948</v>
+        <v>193.2052750345779</v>
       </c>
       <c r="Q26">
-        <v>334.1064328331948</v>
+        <v>329.5052750345779</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07672427538288337</v>
+        <v>0.07705041405384391</v>
       </c>
       <c r="T26">
-        <v>0.7141864984499623</v>
+        <v>0.7217185693728384</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>2.791274079724165</v>
+        <v>2.679623116535198</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06850971054038293</v>
+        <v>0.0684159477897745</v>
       </c>
       <c r="C27">
-        <v>7966.472665354683</v>
+        <v>7902.341975931882</v>
       </c>
       <c r="D27">
-        <v>10408.77530027531</v>
+        <v>10451.92871624934</v>
       </c>
       <c r="E27">
-        <v>729.3920952381088</v>
+        <v>836.6762006349343</v>
       </c>
       <c r="F27">
-        <v>2682.10263492063</v>
+        <v>2789.386740317456</v>
       </c>
       <c r="G27">
         <v>239.8</v>
@@ -3507,28 +3507,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M27">
-        <v>155.0255322984125</v>
+        <v>161.226553590349</v>
       </c>
       <c r="N27">
-        <v>260.3844677015875</v>
+        <v>254.1834464096509</v>
       </c>
       <c r="O27">
-        <v>67.17919266700957</v>
+        <v>65.57932917368994</v>
       </c>
       <c r="P27">
-        <v>193.2052750345779</v>
+        <v>188.604117235961</v>
       </c>
       <c r="Q27">
-        <v>329.5052750345779</v>
+        <v>324.904117235961</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07705041405384391</v>
+        <v>0.07738536728347906</v>
       </c>
       <c r="T27">
-        <v>0.7217185693728384</v>
+        <v>0.7294542097801165</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.679623116535198</v>
+        <v>2.576560688976151</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0684159477897745</v>
+        <v>0.06902337503916606</v>
       </c>
       <c r="C28">
-        <v>7902.341975931882</v>
+        <v>7521.678729895904</v>
       </c>
       <c r="D28">
-        <v>10451.92871624934</v>
+        <v>10178.54957561019</v>
       </c>
       <c r="E28">
-        <v>836.6762006349343</v>
+        <v>943.9603060317593</v>
       </c>
       <c r="F28">
-        <v>2789.386740317456</v>
+        <v>2896.670845714281</v>
       </c>
       <c r="G28">
         <v>239.8</v>
@@ -3589,45 +3589,45 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M28">
-        <v>161.226553590349</v>
+        <v>177.5659228422854</v>
       </c>
       <c r="N28">
-        <v>254.1834464096509</v>
+        <v>237.8440771577145</v>
       </c>
       <c r="O28">
-        <v>65.57932917368994</v>
+        <v>61.36377190669034</v>
       </c>
       <c r="P28">
-        <v>188.604117235961</v>
+        <v>176.4803052510241</v>
       </c>
       <c r="Q28">
-        <v>324.904117235961</v>
+        <v>312.7803052510242</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07738536728347906</v>
+        <v>0.07772949731392612</v>
       </c>
       <c r="T28">
-        <v>0.7294542097801165</v>
+        <v>0.7374017855410189</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.0428876</v>
+        <v>0.0454846</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.576560688976151</v>
+        <v>2.339469157992484</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06902337503916606</v>
+        <v>0.06895558228855764</v>
       </c>
       <c r="C29">
-        <v>7521.678729895904</v>
+        <v>7444.194431056988</v>
       </c>
       <c r="D29">
-        <v>10178.54957561019</v>
+        <v>10208.34938216809</v>
       </c>
       <c r="E29">
-        <v>943.9603060317593</v>
+        <v>1051.244411428585</v>
       </c>
       <c r="F29">
-        <v>2896.670845714281</v>
+        <v>3003.954951111106</v>
       </c>
       <c r="G29">
         <v>239.8</v>
@@ -3671,28 +3671,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M29">
-        <v>177.5659228422854</v>
+        <v>184.1424385031108</v>
       </c>
       <c r="N29">
-        <v>237.8440771577145</v>
+        <v>231.2675614968891</v>
       </c>
       <c r="O29">
-        <v>61.36377190669034</v>
+        <v>59.66703086619739</v>
       </c>
       <c r="P29">
-        <v>176.4803052510241</v>
+        <v>171.6005306306917</v>
       </c>
       <c r="Q29">
-        <v>312.7803052510242</v>
+        <v>307.9005306306917</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07772949731392612</v>
+        <v>0.07808318651188562</v>
       </c>
       <c r="T29">
-        <v>0.7374017855410189</v>
+        <v>0.7455701272952795</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.339469157992484</v>
+        <v>2.255916688064181</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06895558228855764</v>
+        <v>0.06949029353794919</v>
       </c>
       <c r="C30">
-        <v>7444.194431056988</v>
+        <v>7106.498691307863</v>
       </c>
       <c r="D30">
-        <v>10208.34938216809</v>
+        <v>9977.937747815795</v>
       </c>
       <c r="E30">
-        <v>1051.244411428585</v>
+        <v>1158.52851682541</v>
       </c>
       <c r="F30">
-        <v>3003.954951111106</v>
+        <v>3111.239056507932</v>
       </c>
       <c r="G30">
         <v>239.8</v>
@@ -3753,45 +3753,45 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M30">
-        <v>184.1424385031108</v>
+        <v>199.4304235221584</v>
       </c>
       <c r="N30">
-        <v>231.2675614968891</v>
+        <v>215.9795764778415</v>
       </c>
       <c r="O30">
-        <v>59.66703086619739</v>
+        <v>55.7227307312831</v>
       </c>
       <c r="P30">
-        <v>171.6005306306917</v>
+        <v>160.2568457465584</v>
       </c>
       <c r="Q30">
-        <v>307.9005306306917</v>
+        <v>296.5568457465584</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.07808318651188562</v>
+        <v>0.07844683878584394</v>
       </c>
       <c r="T30">
-        <v>0.7455701272952795</v>
+        <v>0.7539685631834628</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.0454846</v>
+        <v>0.04756220000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.255916688064181</v>
+        <v>2.082982088005465</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06949029353794919</v>
+        <v>0.06944327678734077</v>
       </c>
       <c r="C31">
-        <v>7106.498691307863</v>
+        <v>7019.056599135133</v>
       </c>
       <c r="D31">
-        <v>9977.937747815795</v>
+        <v>9997.77976103989</v>
       </c>
       <c r="E31">
-        <v>1158.528516825409</v>
+        <v>1265.812622222235</v>
       </c>
       <c r="F31">
-        <v>3111.239056507931</v>
+        <v>3218.523161904756</v>
       </c>
       <c r="G31">
         <v>239.8</v>
@@ -3835,28 +3835,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M31">
-        <v>199.4304235221584</v>
+        <v>206.3073346780949</v>
       </c>
       <c r="N31">
-        <v>215.9795764778415</v>
+        <v>209.102665321905</v>
       </c>
       <c r="O31">
-        <v>55.72273073128311</v>
+        <v>53.94848765305149</v>
       </c>
       <c r="P31">
-        <v>160.2568457465584</v>
+        <v>155.1541776688535</v>
       </c>
       <c r="Q31">
-        <v>296.5568457465585</v>
+        <v>291.4541776688535</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.07844683878584394</v>
+        <v>0.07882088112477253</v>
       </c>
       <c r="T31">
-        <v>0.7539685631834628</v>
+        <v>0.7626069543827373</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.082982088005466</v>
+        <v>2.013549351738617</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06944327678734077</v>
+        <v>0.07208749403673234</v>
       </c>
       <c r="C32">
-        <v>7019.056599135133</v>
+        <v>5906.111715924368</v>
       </c>
       <c r="D32">
-        <v>9997.77976103989</v>
+        <v>8992.11898322595</v>
       </c>
       <c r="E32">
-        <v>1265.812622222235</v>
+        <v>1373.09672761906</v>
       </c>
       <c r="F32">
-        <v>3218.523161904756</v>
+        <v>3325.807267301582</v>
       </c>
       <c r="G32">
         <v>239.8</v>
@@ -3917,45 +3917,45 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M32">
-        <v>206.3073346780949</v>
+        <v>252.0961908614599</v>
       </c>
       <c r="N32">
-        <v>209.102665321905</v>
+        <v>163.31380913854</v>
       </c>
       <c r="O32">
-        <v>53.94848765305149</v>
+        <v>42.13496275774332</v>
       </c>
       <c r="P32">
-        <v>155.1541776688535</v>
+        <v>121.1788463807967</v>
       </c>
       <c r="Q32">
-        <v>291.4541776688535</v>
+        <v>257.4788463807967</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.07882088112477253</v>
+        <v>0.07920576527062659</v>
       </c>
       <c r="T32">
-        <v>0.7626069543827373</v>
+        <v>0.7714957337327154</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V32">
         <v>0.258</v>
       </c>
       <c r="W32">
-        <v>0.04756220000000001</v>
+        <v>0.0562436</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y32">
-        <v>2.013549351738617</v>
+        <v>1.647823390668721</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07208749403673234</v>
+        <v>0.0721272912861239</v>
       </c>
       <c r="C33">
-        <v>5906.111715924368</v>
+        <v>5785.234810651367</v>
       </c>
       <c r="D33">
-        <v>8992.11898322595</v>
+        <v>8978.526183349775</v>
       </c>
       <c r="E33">
-        <v>1373.09672761906</v>
+        <v>1480.380833015886</v>
       </c>
       <c r="F33">
-        <v>3325.807267301582</v>
+        <v>3433.091372698407</v>
       </c>
       <c r="G33">
         <v>239.8</v>
@@ -3999,28 +3999,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M33">
-        <v>252.0961908614599</v>
+        <v>260.2283260505393</v>
       </c>
       <c r="N33">
-        <v>163.31380913854</v>
+        <v>155.1816739494606</v>
       </c>
       <c r="O33">
-        <v>42.13496275774332</v>
+        <v>40.03687187896084</v>
       </c>
       <c r="P33">
-        <v>121.1788463807967</v>
+        <v>115.1448020704998</v>
       </c>
       <c r="Q33">
-        <v>257.4788463807967</v>
+        <v>251.4448020704998</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.07920576527062659</v>
+        <v>0.07960196953841751</v>
       </c>
       <c r="T33">
-        <v>0.7714957337327154</v>
+        <v>0.7806459477694575</v>
       </c>
       <c r="U33">
         <v>0.07580000000000001</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.647823390668721</v>
+        <v>1.596328909710323</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0721272912861239</v>
+        <v>0.07216708853551548</v>
       </c>
       <c r="C34">
-        <v>5785.234810651367</v>
+        <v>5664.398938050274</v>
       </c>
       <c r="D34">
-        <v>8978.526183349775</v>
+        <v>8964.974416145507</v>
       </c>
       <c r="E34">
-        <v>1480.380833015886</v>
+        <v>1587.664938412711</v>
       </c>
       <c r="F34">
-        <v>3433.091372698407</v>
+        <v>3540.375478095232</v>
       </c>
       <c r="G34">
         <v>239.8</v>
@@ -4081,28 +4081,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M34">
-        <v>260.2283260505393</v>
+        <v>268.3604612396186</v>
       </c>
       <c r="N34">
-        <v>155.1816739494606</v>
+        <v>147.0495387603813</v>
       </c>
       <c r="O34">
-        <v>40.03687187896084</v>
+        <v>37.93878100017837</v>
       </c>
       <c r="P34">
-        <v>115.1448020704998</v>
+        <v>109.1107577602029</v>
       </c>
       <c r="Q34">
-        <v>251.4448020704998</v>
+        <v>245.4107577602029</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.07960196953841751</v>
+        <v>0.08001000079927684</v>
       </c>
       <c r="T34">
-        <v>0.7806459477694575</v>
+        <v>0.7900693025237142</v>
       </c>
       <c r="U34">
         <v>0.07580000000000001</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.596328909710323</v>
+        <v>1.547955306385768</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07216708853551548</v>
+        <v>0.07220688578490705</v>
       </c>
       <c r="C35">
-        <v>5664.398938050274</v>
+        <v>5543.60391260273</v>
       </c>
       <c r="D35">
-        <v>8964.974416145507</v>
+        <v>8951.463496094788</v>
       </c>
       <c r="E35">
-        <v>1587.664938412711</v>
+        <v>1694.949043809536</v>
       </c>
       <c r="F35">
-        <v>3540.375478095232</v>
+        <v>3647.659583492058</v>
       </c>
       <c r="G35">
         <v>239.8</v>
@@ -4163,28 +4163,28 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M35">
-        <v>268.3604612396186</v>
+        <v>276.492596428698</v>
       </c>
       <c r="N35">
-        <v>147.0495387603813</v>
+        <v>138.9174035713019</v>
       </c>
       <c r="O35">
-        <v>37.93878100017837</v>
+        <v>35.84069012139589</v>
       </c>
       <c r="P35">
-        <v>109.1107577602029</v>
+        <v>103.076713449906</v>
       </c>
       <c r="Q35">
-        <v>245.4107577602029</v>
+        <v>239.376713449906</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08001000079927684</v>
+        <v>0.08043039664379856</v>
       </c>
       <c r="T35">
-        <v>0.7900693025237142</v>
+        <v>0.7997782134826454</v>
       </c>
       <c r="U35">
         <v>0.07580000000000001</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.547955306385768</v>
+        <v>1.502427209139128</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07220688578490705</v>
+        <v>0.08423354901608696</v>
       </c>
       <c r="C36">
-        <v>5543.60391260273</v>
+        <v>2635.219215411192</v>
       </c>
       <c r="D36">
-        <v>8951.463496094788</v>
+        <v>6150.362904300075</v>
       </c>
       <c r="E36">
-        <v>1694.949043809536</v>
+        <v>1802.233149206362</v>
       </c>
       <c r="F36">
-        <v>3647.659583492058</v>
+        <v>3754.943688888883</v>
       </c>
       <c r="G36">
         <v>239.8</v>
@@ -4245,45 +4245,45 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M36">
-        <v>276.492596428698</v>
+        <v>445.3363215022216</v>
       </c>
       <c r="N36">
-        <v>138.9174035713019</v>
+        <v>-29.92632150222164</v>
       </c>
       <c r="O36">
-        <v>35.84069012139589</v>
+        <v>-7.720990947573183</v>
       </c>
       <c r="P36">
-        <v>103.076713449906</v>
+        <v>-22.20533055464846</v>
       </c>
       <c r="Q36">
-        <v>239.376713449906</v>
+        <v>114.0946694453516</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08043039664379856</v>
+        <v>0.08109761839514129</v>
       </c>
       <c r="T36">
-        <v>0.7997782134826454</v>
+        <v>0.8151874918046484</v>
       </c>
       <c r="U36">
-        <v>0.07580000000000001</v>
+        <v>0.1186</v>
       </c>
       <c r="V36">
-        <v>0.258</v>
+        <v>0.2406625618105245</v>
       </c>
       <c r="W36">
-        <v>0.0562436</v>
+        <v>0.0900574201692718</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y36">
-        <v>1.502427209139128</v>
+        <v>0.9328006271725753</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08423354901608696</v>
+        <v>0.08496154901608696</v>
       </c>
       <c r="C37">
-        <v>2635.219215411192</v>
+        <v>2413.601936102088</v>
       </c>
       <c r="D37">
-        <v>6150.362904300075</v>
+        <v>6036.029730387796</v>
       </c>
       <c r="E37">
-        <v>1802.233149206362</v>
+        <v>1909.517254603187</v>
       </c>
       <c r="F37">
-        <v>3754.943688888883</v>
+        <v>3862.227794285708</v>
       </c>
       <c r="G37">
         <v>239.8</v>
@@ -4327,37 +4327,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M37">
-        <v>445.3363215022216</v>
+        <v>458.0602164022851</v>
       </c>
       <c r="N37">
-        <v>-29.92632150222164</v>
+        <v>-42.65021640228514</v>
       </c>
       <c r="O37">
-        <v>-7.720990947573183</v>
+        <v>-11.00375583178957</v>
       </c>
       <c r="P37">
-        <v>-22.20533055464846</v>
+        <v>-31.64646057049557</v>
       </c>
       <c r="Q37">
-        <v>114.0946694453516</v>
+        <v>104.6535394295044</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08109761839514129</v>
+        <v>0.08164914368256537</v>
       </c>
       <c r="T37">
-        <v>0.8151874918046484</v>
+        <v>0.8279247963640962</v>
       </c>
       <c r="U37">
         <v>0.1186</v>
       </c>
       <c r="V37">
-        <v>0.2406625618105245</v>
+        <v>0.233977490649121</v>
       </c>
       <c r="W37">
-        <v>0.0900574201692718</v>
+        <v>0.09085026960901425</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.9328006271725753</v>
+        <v>0.9068894986400038</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08496154901608696</v>
+        <v>0.08568954901608697</v>
       </c>
       <c r="C38">
-        <v>2413.601936102089</v>
+        <v>2196.15790781543</v>
       </c>
       <c r="D38">
-        <v>6036.029730387796</v>
+        <v>5925.869807497963</v>
       </c>
       <c r="E38">
-        <v>1909.517254603186</v>
+        <v>2016.801360000012</v>
       </c>
       <c r="F38">
-        <v>3862.227794285708</v>
+        <v>3969.511899682533</v>
       </c>
       <c r="G38">
         <v>239.8</v>
@@ -4409,37 +4409,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M38">
-        <v>458.060216402285</v>
+        <v>470.7841113023485</v>
       </c>
       <c r="N38">
-        <v>-42.65021640228508</v>
+        <v>-55.37411130234858</v>
       </c>
       <c r="O38">
-        <v>-11.00375583178955</v>
+        <v>-14.28652071600593</v>
       </c>
       <c r="P38">
-        <v>-31.64646057049553</v>
+        <v>-41.08759058634264</v>
       </c>
       <c r="Q38">
-        <v>104.6535394295045</v>
+        <v>95.21240941365737</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08164914368256536</v>
+        <v>0.08221817770927276</v>
       </c>
       <c r="T38">
-        <v>0.827924796364096</v>
+        <v>0.8410664597984469</v>
       </c>
       <c r="U38">
         <v>0.1186</v>
       </c>
       <c r="V38">
-        <v>0.233977490649121</v>
+        <v>0.2276537746856312</v>
       </c>
       <c r="W38">
-        <v>0.09085026960901425</v>
+        <v>0.09160026232228415</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9068894986400039</v>
+        <v>0.8823789716497334</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08568954901608697</v>
+        <v>0.08641754901608698</v>
       </c>
       <c r="C39">
-        <v>2196.15790781543</v>
+        <v>1982.662735420201</v>
       </c>
       <c r="D39">
-        <v>5925.869807497963</v>
+        <v>5819.658740499559</v>
       </c>
       <c r="E39">
-        <v>2016.801360000012</v>
+        <v>2124.085465396836</v>
       </c>
       <c r="F39">
-        <v>3969.511899682533</v>
+        <v>4076.796005079358</v>
       </c>
       <c r="G39">
         <v>239.8</v>
@@ -4491,37 +4491,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M39">
-        <v>470.7841113023485</v>
+        <v>483.5080062024119</v>
       </c>
       <c r="N39">
-        <v>-55.37411130234858</v>
+        <v>-68.09800620241202</v>
       </c>
       <c r="O39">
-        <v>-14.28652071600593</v>
+        <v>-17.5692856002223</v>
       </c>
       <c r="P39">
-        <v>-41.08759058634264</v>
+        <v>-50.52872060218972</v>
       </c>
       <c r="Q39">
-        <v>95.21240941365737</v>
+        <v>85.77127939781029</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08221817770927276</v>
+        <v>0.08280556767232554</v>
       </c>
       <c r="T39">
-        <v>0.8410664597984469</v>
+        <v>0.8546320478597121</v>
       </c>
       <c r="U39">
         <v>0.1186</v>
       </c>
       <c r="V39">
-        <v>0.2276537746856312</v>
+        <v>0.2216628858781146</v>
       </c>
       <c r="W39">
-        <v>0.09160026232228415</v>
+        <v>0.09231078173485562</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8823789716497334</v>
+        <v>0.8591584723957931</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08641754901608698</v>
+        <v>0.08714554901608698</v>
       </c>
       <c r="C40">
-        <v>1982.662735420201</v>
+        <v>1772.907828113471</v>
       </c>
       <c r="D40">
-        <v>5819.658740499559</v>
+        <v>5717.187938589655</v>
       </c>
       <c r="E40">
-        <v>2124.085465396836</v>
+        <v>2231.369570793662</v>
       </c>
       <c r="F40">
-        <v>4076.796005079358</v>
+        <v>4184.080110476184</v>
       </c>
       <c r="G40">
         <v>239.8</v>
@@ -4573,37 +4573,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M40">
-        <v>483.5080062024119</v>
+        <v>496.2319011024755</v>
       </c>
       <c r="N40">
-        <v>-68.09800620241202</v>
+        <v>-80.82190110247558</v>
       </c>
       <c r="O40">
-        <v>-17.5692856002223</v>
+        <v>-20.8520504844387</v>
       </c>
       <c r="P40">
-        <v>-50.52872060218972</v>
+        <v>-59.96985061803688</v>
       </c>
       <c r="Q40">
-        <v>85.77127939781029</v>
+        <v>76.33014938196314</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08280556767232554</v>
+        <v>0.08341221632269154</v>
       </c>
       <c r="T40">
-        <v>0.8546320478597121</v>
+        <v>0.8686424093000353</v>
       </c>
       <c r="U40">
         <v>0.1186</v>
       </c>
       <c r="V40">
-        <v>0.2216628858781146</v>
+        <v>0.2159792221376501</v>
       </c>
       <c r="W40">
-        <v>0.09231078173485562</v>
+        <v>0.09298486425447471</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8591584723957931</v>
+        <v>0.837128767975388</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08714554901608698</v>
+        <v>0.08787354901608696</v>
       </c>
       <c r="C41">
-        <v>1772.907828113471</v>
+        <v>1566.699032106359</v>
       </c>
       <c r="D41">
-        <v>5717.187938589655</v>
+        <v>5618.263247979367</v>
       </c>
       <c r="E41">
-        <v>2231.369570793662</v>
+        <v>2338.653676190487</v>
       </c>
       <c r="F41">
-        <v>4184.080110476184</v>
+        <v>4291.364215873009</v>
       </c>
       <c r="G41">
         <v>239.8</v>
@@ -4655,37 +4655,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M41">
-        <v>496.2319011024755</v>
+        <v>508.9557960025389</v>
       </c>
       <c r="N41">
-        <v>-80.82190110247558</v>
+        <v>-93.54579600253902</v>
       </c>
       <c r="O41">
-        <v>-20.8520504844387</v>
+        <v>-24.13481536865507</v>
       </c>
       <c r="P41">
-        <v>-59.96985061803688</v>
+        <v>-69.41098063388395</v>
       </c>
       <c r="Q41">
-        <v>76.33014938196314</v>
+        <v>66.88901936611606</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08341221632269154</v>
+        <v>0.08403908659473638</v>
       </c>
       <c r="T41">
-        <v>0.8686424093000353</v>
+        <v>0.8831197827883692</v>
       </c>
       <c r="U41">
         <v>0.1186</v>
       </c>
       <c r="V41">
-        <v>0.2159792221376501</v>
+        <v>0.2105797415842089</v>
       </c>
       <c r="W41">
-        <v>0.09298486425447471</v>
+        <v>0.09362524264811284</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.837128767975388</v>
+        <v>0.8162005487760033</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08787354901608696</v>
+        <v>0.1231674380004864</v>
       </c>
       <c r="C42">
-        <v>1566.699032106359</v>
+        <v>-1103.554256244006</v>
       </c>
       <c r="D42">
-        <v>5618.263247979367</v>
+        <v>3055.294065025828</v>
       </c>
       <c r="E42">
-        <v>2338.653676190487</v>
+        <v>2445.937781587312</v>
       </c>
       <c r="F42">
-        <v>4291.364215873009</v>
+        <v>4398.648321269834</v>
       </c>
       <c r="G42">
         <v>239.8</v>
@@ -4737,45 +4737,45 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M42">
-        <v>508.9557960025389</v>
+        <v>883.2485829109827</v>
       </c>
       <c r="N42">
-        <v>-93.54579600253902</v>
+        <v>-467.8385829109828</v>
       </c>
       <c r="O42">
-        <v>-24.13481536865507</v>
+        <v>-120.7023543910336</v>
       </c>
       <c r="P42">
-        <v>-69.41098063388395</v>
+        <v>-347.1362285199492</v>
       </c>
       <c r="Q42">
-        <v>66.88901936611606</v>
+        <v>-210.8362285199492</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08403908659473638</v>
+        <v>0.08615142532413773</v>
       </c>
       <c r="T42">
-        <v>0.8831197827883692</v>
+        <v>0.9319035871625342</v>
       </c>
       <c r="U42">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.2105797415842089</v>
+        <v>0.1213427137881993</v>
       </c>
       <c r="W42">
-        <v>0.09362524264811284</v>
+        <v>0.1764343830713296</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.8162005487760033</v>
+        <v>0.4703205960782918</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1231674380004864</v>
+        <v>0.1247174380004864</v>
       </c>
       <c r="C43">
-        <v>-1103.554256244006</v>
+        <v>-1270.846718738801</v>
       </c>
       <c r="D43">
-        <v>3055.294065025828</v>
+        <v>2995.285707927859</v>
       </c>
       <c r="E43">
-        <v>2445.937781587312</v>
+        <v>2553.221886984138</v>
       </c>
       <c r="F43">
-        <v>4398.648321269834</v>
+        <v>4505.93242666666</v>
       </c>
       <c r="G43">
         <v>239.8</v>
@@ -4819,37 +4819,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M43">
-        <v>883.2485829109827</v>
+        <v>904.7912312746654</v>
       </c>
       <c r="N43">
-        <v>-467.8385829109828</v>
+        <v>-489.3812312746655</v>
       </c>
       <c r="O43">
-        <v>-120.7023543910336</v>
+        <v>-126.2603576688637</v>
       </c>
       <c r="P43">
-        <v>-347.1362285199492</v>
+        <v>-363.1208736058018</v>
       </c>
       <c r="Q43">
-        <v>-210.8362285199492</v>
+        <v>-226.8208736058018</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08615142532413773</v>
+        <v>0.08684713955386425</v>
       </c>
       <c r="T43">
-        <v>0.9319035871625342</v>
+        <v>0.9479708903894745</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.1213427137881993</v>
+        <v>0.1184536015551469</v>
       </c>
       <c r="W43">
-        <v>0.1764343830713296</v>
+        <v>0.1770145168077265</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.4703205960782918</v>
+        <v>0.4591224866478562</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1247174380004864</v>
+        <v>0.1262674380004864</v>
       </c>
       <c r="C44">
-        <v>-1270.8467187388</v>
+        <v>-1435.82736527889</v>
       </c>
       <c r="D44">
-        <v>2995.285707927859</v>
+        <v>2937.589166784594</v>
       </c>
       <c r="E44">
-        <v>2553.221886984137</v>
+        <v>2660.505992380962</v>
       </c>
       <c r="F44">
-        <v>4505.932426666659</v>
+        <v>4613.216532063484</v>
       </c>
       <c r="G44">
         <v>239.8</v>
@@ -4901,37 +4901,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M44">
-        <v>904.7912312746652</v>
+        <v>926.3338796383476</v>
       </c>
       <c r="N44">
-        <v>-489.3812312746653</v>
+        <v>-510.9238796383477</v>
       </c>
       <c r="O44">
-        <v>-126.2603576688636</v>
+        <v>-131.8183609466937</v>
       </c>
       <c r="P44">
-        <v>-363.1208736058016</v>
+        <v>-379.105518691654</v>
       </c>
       <c r="Q44">
-        <v>-226.8208736058016</v>
+        <v>-242.805518691654</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08684713955386425</v>
+        <v>0.08756726480919519</v>
       </c>
       <c r="T44">
-        <v>0.9479708903894744</v>
+        <v>0.9646019586419213</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.1184536015551469</v>
+        <v>0.1156988666352598</v>
       </c>
       <c r="W44">
-        <v>0.1770145168077265</v>
+        <v>0.1775676675796398</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.4591224866478563</v>
+        <v>0.4484452195165108</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1262674380004864</v>
+        <v>0.1278174380004864</v>
       </c>
       <c r="C45">
-        <v>-1435.82736527889</v>
+        <v>-1598.62726487169</v>
       </c>
       <c r="D45">
-        <v>2937.589166784594</v>
+        <v>2882.073372588619</v>
       </c>
       <c r="E45">
-        <v>2660.505992380962</v>
+        <v>2767.790097777788</v>
       </c>
       <c r="F45">
-        <v>4613.216532063484</v>
+        <v>4720.50063746031</v>
       </c>
       <c r="G45">
         <v>239.8</v>
@@ -4983,37 +4983,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M45">
-        <v>926.3338796383476</v>
+        <v>947.8765280020302</v>
       </c>
       <c r="N45">
-        <v>-510.9238796383477</v>
+        <v>-532.4665280020304</v>
       </c>
       <c r="O45">
-        <v>-131.8183609466937</v>
+        <v>-137.3763642245238</v>
       </c>
       <c r="P45">
-        <v>-379.105518691654</v>
+        <v>-395.0901637775065</v>
       </c>
       <c r="Q45">
-        <v>-242.805518691654</v>
+        <v>-258.7901637775065</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08756726480919519</v>
+        <v>0.08831310882364511</v>
       </c>
       <c r="T45">
-        <v>0.9646019586419213</v>
+        <v>0.9818269936176699</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.1156988666352598</v>
+        <v>0.1130693469390039</v>
       </c>
       <c r="W45">
-        <v>0.1775676675796398</v>
+        <v>0.178095675134648</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.4484452195165108</v>
+        <v>0.4382532827093173</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1278174380004864</v>
+        <v>0.1293674380004864</v>
       </c>
       <c r="C46">
-        <v>-1598.62726487169</v>
+        <v>-1759.367762308276</v>
       </c>
       <c r="D46">
-        <v>2882.073372588619</v>
+        <v>2828.616980548858</v>
       </c>
       <c r="E46">
-        <v>2767.790097777788</v>
+        <v>2875.074203174613</v>
       </c>
       <c r="F46">
-        <v>4720.50063746031</v>
+        <v>4827.784742857135</v>
       </c>
       <c r="G46">
         <v>239.8</v>
@@ -5065,37 +5065,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M46">
-        <v>947.8765280020302</v>
+        <v>969.4191763657127</v>
       </c>
       <c r="N46">
-        <v>-532.4665280020304</v>
+        <v>-554.0091763657128</v>
       </c>
       <c r="O46">
-        <v>-137.3763642245238</v>
+        <v>-142.9343675023539</v>
       </c>
       <c r="P46">
-        <v>-395.0901637775065</v>
+        <v>-411.074808863359</v>
       </c>
       <c r="Q46">
-        <v>-258.7901637775065</v>
+        <v>-274.7748088633589</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08831310882364511</v>
+        <v>0.08908607443862047</v>
       </c>
       <c r="T46">
-        <v>0.9818269936176699</v>
+        <v>0.9996783935016275</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.1130693469390039</v>
+        <v>0.1105566947848038</v>
       </c>
       <c r="W46">
-        <v>0.178095675134648</v>
+        <v>0.1786002156872114</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4382532827093173</v>
+        <v>0.4285143208713325</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1293674380004864</v>
+        <v>0.1309174380004864</v>
       </c>
       <c r="C47">
-        <v>-1759.367762308276</v>
+        <v>-1918.161363559824</v>
       </c>
       <c r="D47">
-        <v>2828.616980548858</v>
+        <v>2777.107484694136</v>
       </c>
       <c r="E47">
-        <v>2875.074203174613</v>
+        <v>2982.358308571438</v>
       </c>
       <c r="F47">
-        <v>4827.784742857135</v>
+        <v>4935.06884825396</v>
       </c>
       <c r="G47">
         <v>239.8</v>
@@ -5147,37 +5147,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M47">
-        <v>969.4191763657127</v>
+        <v>990.9618247293952</v>
       </c>
       <c r="N47">
-        <v>-554.0091763657128</v>
+        <v>-575.5518247293953</v>
       </c>
       <c r="O47">
-        <v>-142.9343675023539</v>
+        <v>-148.492370780184</v>
       </c>
       <c r="P47">
-        <v>-411.074808863359</v>
+        <v>-427.0594539492113</v>
       </c>
       <c r="Q47">
-        <v>-274.7748088633589</v>
+        <v>-290.7594539492113</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08908607443862047</v>
+        <v>0.08988766840970604</v>
       </c>
       <c r="T47">
-        <v>0.9996783935016275</v>
+        <v>1.01819095634425</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.1105566947848038</v>
+        <v>0.1081532883764385</v>
       </c>
       <c r="W47">
-        <v>0.1786002156872114</v>
+        <v>0.1790828196940112</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4285143208713325</v>
+        <v>0.4191987921567383</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1309174380004864</v>
+        <v>0.1324674380004864</v>
       </c>
       <c r="C48">
-        <v>-1918.161363559824</v>
+        <v>-2075.112526165054</v>
       </c>
       <c r="D48">
-        <v>2777.107484694136</v>
+        <v>2727.440427485732</v>
       </c>
       <c r="E48">
-        <v>2982.358308571438</v>
+        <v>3089.642413968264</v>
       </c>
       <c r="F48">
-        <v>4935.06884825396</v>
+        <v>5042.352953650786</v>
       </c>
       <c r="G48">
         <v>239.8</v>
@@ -5229,37 +5229,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M48">
-        <v>990.9618247293952</v>
+        <v>1012.504473093078</v>
       </c>
       <c r="N48">
-        <v>-575.5518247293953</v>
+        <v>-597.094473093078</v>
       </c>
       <c r="O48">
-        <v>-148.492370780184</v>
+        <v>-154.0503740580141</v>
       </c>
       <c r="P48">
-        <v>-427.0594539492113</v>
+        <v>-443.0440990350639</v>
       </c>
       <c r="Q48">
-        <v>-290.7594539492113</v>
+        <v>-306.7440990350639</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08988766840970604</v>
+        <v>0.09071951120988918</v>
       </c>
       <c r="T48">
-        <v>1.01819095634425</v>
+        <v>1.037402106463953</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.1081532883764385</v>
+        <v>0.1058521545811951</v>
       </c>
       <c r="W48">
-        <v>0.1790828196940112</v>
+        <v>0.179544887360096</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.4191987921567383</v>
+        <v>0.4102796689193609</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1324674380004864</v>
+        <v>0.1340174380004864</v>
       </c>
       <c r="C49">
-        <v>-2075.112526165054</v>
+        <v>-2230.318366293957</v>
       </c>
       <c r="D49">
-        <v>2727.440427485732</v>
+        <v>2679.518692753653</v>
       </c>
       <c r="E49">
-        <v>3089.642413968264</v>
+        <v>3196.926519365089</v>
       </c>
       <c r="F49">
-        <v>5042.352953650786</v>
+        <v>5149.637059047611</v>
       </c>
       <c r="G49">
         <v>239.8</v>
@@ -5311,37 +5311,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M49">
-        <v>1012.504473093078</v>
+        <v>1034.04712145676</v>
       </c>
       <c r="N49">
-        <v>-597.094473093078</v>
+        <v>-618.6371214567605</v>
       </c>
       <c r="O49">
-        <v>-154.0503740580141</v>
+        <v>-159.6083773358442</v>
       </c>
       <c r="P49">
-        <v>-443.0440990350639</v>
+        <v>-459.0287441209163</v>
       </c>
       <c r="Q49">
-        <v>-306.7440990350639</v>
+        <v>-322.7287441209162</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09071951120988918</v>
+        <v>0.09158334796392552</v>
       </c>
       <c r="T49">
-        <v>1.037402106463953</v>
+        <v>1.057352146972875</v>
       </c>
       <c r="U49">
         <v>0.2008</v>
       </c>
       <c r="V49">
-        <v>0.1058521545811951</v>
+        <v>0.1036469013607536</v>
       </c>
       <c r="W49">
-        <v>0.179544887360096</v>
+        <v>0.1799877022067607</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.4102796689193609</v>
+        <v>0.4017321758168741</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1340174380004864</v>
+        <v>0.1355674380004864</v>
       </c>
       <c r="C50">
-        <v>-2230.318366293955</v>
+        <v>-2383.869292559009</v>
       </c>
       <c r="D50">
-        <v>2679.518692753655</v>
+        <v>2633.251871885427</v>
       </c>
       <c r="E50">
-        <v>3196.926519365088</v>
+        <v>3304.210624761914</v>
       </c>
       <c r="F50">
-        <v>5149.63705904761</v>
+        <v>5256.921164444436</v>
       </c>
       <c r="G50">
         <v>239.8</v>
@@ -5393,37 +5393,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M50">
-        <v>1034.04712145676</v>
+        <v>1055.589769820443</v>
       </c>
       <c r="N50">
-        <v>-618.6371214567603</v>
+        <v>-640.179769820443</v>
       </c>
       <c r="O50">
-        <v>-159.6083773358442</v>
+        <v>-165.1663806136743</v>
       </c>
       <c r="P50">
-        <v>-459.0287441209161</v>
+        <v>-475.0133892067687</v>
       </c>
       <c r="Q50">
-        <v>-322.7287441209161</v>
+        <v>-338.7133892067687</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0915833479639255</v>
+        <v>0.09248106066910053</v>
       </c>
       <c r="T50">
-        <v>1.057352146972875</v>
+        <v>1.078084542011559</v>
       </c>
       <c r="U50">
         <v>0.2008</v>
       </c>
       <c r="V50">
-        <v>0.1036469013607536</v>
+        <v>0.1015316584758402</v>
       </c>
       <c r="W50">
-        <v>0.1799877022067607</v>
+        <v>0.1804124429780513</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4017321758168743</v>
+        <v>0.3935335599838767</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1355674380004864</v>
+        <v>0.1371174380004864</v>
       </c>
       <c r="C51">
-        <v>-2383.869292559009</v>
+        <v>-2535.849575277417</v>
       </c>
       <c r="D51">
-        <v>2633.251871885427</v>
+        <v>2588.555694563844</v>
       </c>
       <c r="E51">
-        <v>3304.210624761914</v>
+        <v>3411.494730158739</v>
       </c>
       <c r="F51">
-        <v>5256.921164444436</v>
+        <v>5364.205269841261</v>
       </c>
       <c r="G51">
         <v>239.8</v>
@@ -5475,37 +5475,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M51">
-        <v>1055.589769820443</v>
+        <v>1077.132418184125</v>
       </c>
       <c r="N51">
-        <v>-640.179769820443</v>
+        <v>-661.7224181841254</v>
       </c>
       <c r="O51">
-        <v>-165.1663806136743</v>
+        <v>-170.7243838915044</v>
       </c>
       <c r="P51">
-        <v>-475.0133892067687</v>
+        <v>-490.9980342926211</v>
       </c>
       <c r="Q51">
-        <v>-338.7133892067687</v>
+        <v>-354.6980342926211</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09248106066910053</v>
+        <v>0.09341468188248253</v>
       </c>
       <c r="T51">
-        <v>1.078084542011559</v>
+        <v>1.09964623285179</v>
       </c>
       <c r="U51">
         <v>0.2008</v>
       </c>
       <c r="V51">
-        <v>0.1015316584758402</v>
+        <v>0.0995010253063234</v>
       </c>
       <c r="W51">
-        <v>0.1804124429780513</v>
+        <v>0.1808201941184903</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3935335599838767</v>
+        <v>0.3856628887841992</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1371174380004864</v>
+        <v>0.1386674380004864</v>
       </c>
       <c r="C52">
-        <v>-2535.849575277417</v>
+        <v>-2686.337858725896</v>
       </c>
       <c r="D52">
-        <v>2588.555694563844</v>
+        <v>2545.35151651219</v>
       </c>
       <c r="E52">
-        <v>3411.494730158739</v>
+        <v>3518.778835555564</v>
       </c>
       <c r="F52">
-        <v>5364.205269841261</v>
+        <v>5471.489375238086</v>
       </c>
       <c r="G52">
         <v>239.8</v>
@@ -5557,37 +5557,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M52">
-        <v>1077.132418184125</v>
+        <v>1098.675066547808</v>
       </c>
       <c r="N52">
-        <v>-661.7224181841254</v>
+        <v>-683.2650665478079</v>
       </c>
       <c r="O52">
-        <v>-170.7243838915044</v>
+        <v>-176.2823871693344</v>
       </c>
       <c r="P52">
-        <v>-490.9980342926211</v>
+        <v>-506.9826793784734</v>
       </c>
       <c r="Q52">
-        <v>-354.6980342926211</v>
+        <v>-370.6826793784734</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09341468188248253</v>
+        <v>0.09438641008416584</v>
       </c>
       <c r="T52">
-        <v>1.09964623285179</v>
+        <v>1.122087992705909</v>
       </c>
       <c r="U52">
         <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.0995010253063234</v>
+        <v>0.097550024810121</v>
       </c>
       <c r="W52">
-        <v>0.1808201941184903</v>
+        <v>0.1812119550181277</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3856628887841992</v>
+        <v>0.3781008713570581</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1386674380004864</v>
+        <v>0.1402174380004864</v>
       </c>
       <c r="C53">
-        <v>-2686.337858725896</v>
+        <v>-2835.407622938985</v>
       </c>
       <c r="D53">
-        <v>2545.35151651219</v>
+        <v>2503.565857695926</v>
       </c>
       <c r="E53">
-        <v>3518.778835555564</v>
+        <v>3626.06294095239</v>
       </c>
       <c r="F53">
-        <v>5471.489375238086</v>
+        <v>5578.773480634912</v>
       </c>
       <c r="G53">
         <v>239.8</v>
@@ -5639,37 +5639,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M53">
-        <v>1098.675066547808</v>
+        <v>1120.21771491149</v>
       </c>
       <c r="N53">
-        <v>-683.2650665478079</v>
+        <v>-704.8077149114904</v>
       </c>
       <c r="O53">
-        <v>-176.2823871693344</v>
+        <v>-181.8403904471645</v>
       </c>
       <c r="P53">
-        <v>-506.9826793784734</v>
+        <v>-522.9673244643259</v>
       </c>
       <c r="Q53">
-        <v>-370.6826793784734</v>
+        <v>-386.6673244643259</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09438641008416584</v>
+        <v>0.0953986269609193</v>
       </c>
       <c r="T53">
-        <v>1.122087992705909</v>
+        <v>1.145464825887282</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.097550024810121</v>
+        <v>0.09567406279454174</v>
       </c>
       <c r="W53">
-        <v>0.1812119550181277</v>
+        <v>0.181588648190856</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3781008713570581</v>
+        <v>0.3708297007540378</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1402174380004864</v>
+        <v>0.1417674380004864</v>
       </c>
       <c r="C54">
-        <v>-2835.407622938985</v>
+        <v>-2983.127600755463</v>
       </c>
       <c r="D54">
-        <v>2503.565857695926</v>
+        <v>2463.129985276273</v>
       </c>
       <c r="E54">
-        <v>3626.06294095239</v>
+        <v>3733.347046349215</v>
       </c>
       <c r="F54">
-        <v>5578.773480634912</v>
+        <v>5686.057586031737</v>
       </c>
       <c r="G54">
         <v>239.8</v>
@@ -5721,37 +5721,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M54">
-        <v>1120.21771491149</v>
+        <v>1141.760363275173</v>
       </c>
       <c r="N54">
-        <v>-704.8077149114904</v>
+        <v>-726.3503632751729</v>
       </c>
       <c r="O54">
-        <v>-181.8403904471645</v>
+        <v>-187.3983937249946</v>
       </c>
       <c r="P54">
-        <v>-522.9673244643259</v>
+        <v>-538.9519695501783</v>
       </c>
       <c r="Q54">
-        <v>-386.6673244643259</v>
+        <v>-402.6519695501783</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.0953986269609193</v>
+        <v>0.09645391689625801</v>
       </c>
       <c r="T54">
-        <v>1.145464825887282</v>
+        <v>1.169836417927437</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.09567406279454174</v>
+        <v>0.09386889179841833</v>
       </c>
       <c r="W54">
-        <v>0.181588648190856</v>
+        <v>0.1819511265268776</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3708297007540378</v>
+        <v>0.3638329139473577</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1417674380004864</v>
+        <v>0.1433174380004864</v>
       </c>
       <c r="C55">
-        <v>-2983.127600755463</v>
+        <v>-3129.562155092089</v>
       </c>
       <c r="D55">
-        <v>2463.129985276273</v>
+        <v>2423.979536336472</v>
       </c>
       <c r="E55">
-        <v>3733.347046349215</v>
+        <v>3840.63115174604</v>
       </c>
       <c r="F55">
-        <v>5686.057586031737</v>
+        <v>5793.341691428562</v>
       </c>
       <c r="G55">
         <v>239.8</v>
@@ -5803,37 +5803,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M55">
-        <v>1141.760363275173</v>
+        <v>1163.303011638855</v>
       </c>
       <c r="N55">
-        <v>-726.3503632751729</v>
+        <v>-747.8930116388553</v>
       </c>
       <c r="O55">
-        <v>-187.3983937249946</v>
+        <v>-192.9563970028247</v>
       </c>
       <c r="P55">
-        <v>-538.9519695501783</v>
+        <v>-554.9366146360306</v>
       </c>
       <c r="Q55">
-        <v>-402.6519695501783</v>
+        <v>-418.6366146360306</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09645391689625801</v>
+        <v>0.09755508900269841</v>
       </c>
       <c r="T55">
-        <v>1.169836417927437</v>
+        <v>1.19526764440412</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.09386889179841833</v>
+        <v>0.09213057898733651</v>
       </c>
       <c r="W55">
-        <v>0.1819511265268776</v>
+        <v>0.1823001797393428</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3638329139473577</v>
+        <v>0.3570952673927771</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1433174380004864</v>
+        <v>0.1448674380004864</v>
       </c>
       <c r="C56">
-        <v>-3129.562155092089</v>
+        <v>-3274.771620800575</v>
       </c>
       <c r="D56">
-        <v>2423.979536336472</v>
+        <v>2386.054176024812</v>
       </c>
       <c r="E56">
-        <v>3840.63115174604</v>
+        <v>3947.915257142866</v>
       </c>
       <c r="F56">
-        <v>5793.341691428562</v>
+        <v>5900.625796825388</v>
       </c>
       <c r="G56">
         <v>239.8</v>
@@ -5885,37 +5885,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M56">
-        <v>1163.303011638855</v>
+        <v>1184.845660002538</v>
       </c>
       <c r="N56">
-        <v>-747.8930116388553</v>
+        <v>-769.435660002538</v>
       </c>
       <c r="O56">
-        <v>-192.9563970028247</v>
+        <v>-198.5144002806548</v>
       </c>
       <c r="P56">
-        <v>-554.9366146360306</v>
+        <v>-570.9212597218832</v>
       </c>
       <c r="Q56">
-        <v>-418.6366146360306</v>
+        <v>-434.6212597218832</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09755508900269841</v>
+        <v>0.09870520209164726</v>
       </c>
       <c r="T56">
-        <v>1.19526764440412</v>
+        <v>1.2218291476131</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.09213057898733651</v>
+        <v>0.0904554775512031</v>
       </c>
       <c r="W56">
-        <v>0.1823001797393428</v>
+        <v>0.1826365401077184</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3570952673927771</v>
+        <v>0.3506026261674537</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1448674380004864</v>
+        <v>0.1464174380004864</v>
       </c>
       <c r="C57">
-        <v>-3274.771620800575</v>
+        <v>-3418.812614926971</v>
       </c>
       <c r="D57">
-        <v>2386.054176024812</v>
+        <v>2349.297287295241</v>
       </c>
       <c r="E57">
-        <v>3947.915257142866</v>
+        <v>4055.199362539691</v>
       </c>
       <c r="F57">
-        <v>5900.625796825388</v>
+        <v>6007.909902222213</v>
       </c>
       <c r="G57">
         <v>239.8</v>
@@ -5967,37 +5967,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M57">
-        <v>1184.845660002538</v>
+        <v>1206.38830836622</v>
       </c>
       <c r="N57">
-        <v>-769.435660002538</v>
+        <v>-790.9783083662205</v>
       </c>
       <c r="O57">
-        <v>-198.5144002806548</v>
+        <v>-204.0724035584849</v>
       </c>
       <c r="P57">
-        <v>-570.9212597218832</v>
+        <v>-586.9059048077356</v>
       </c>
       <c r="Q57">
-        <v>-434.6212597218832</v>
+        <v>-450.6059048077356</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09870520209164726</v>
+        <v>0.09990759304827562</v>
       </c>
       <c r="T57">
-        <v>1.2218291476131</v>
+        <v>1.249597991877035</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.0904554775512031</v>
+        <v>0.08884020116636018</v>
       </c>
       <c r="W57">
-        <v>0.1826365401077184</v>
+        <v>0.1829608876057949</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3506026261674537</v>
+        <v>0.3443418649858921</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1464174380004864</v>
+        <v>0.1479674380004864</v>
       </c>
       <c r="C58">
-        <v>-3418.812614926971</v>
+        <v>-3561.738318729057</v>
       </c>
       <c r="D58">
-        <v>2349.297287295241</v>
+        <v>2313.655688889981</v>
       </c>
       <c r="E58">
-        <v>4055.199362539691</v>
+        <v>4162.483467936516</v>
       </c>
       <c r="F58">
-        <v>6007.909902222213</v>
+        <v>6115.194007619038</v>
       </c>
       <c r="G58">
         <v>239.8</v>
@@ -6049,37 +6049,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M58">
-        <v>1206.38830836622</v>
+        <v>1227.930956729903</v>
       </c>
       <c r="N58">
-        <v>-790.9783083662205</v>
+        <v>-812.520956729903</v>
       </c>
       <c r="O58">
-        <v>-204.0724035584849</v>
+        <v>-209.630406836315</v>
       </c>
       <c r="P58">
-        <v>-586.9059048077356</v>
+        <v>-602.8905498935881</v>
       </c>
       <c r="Q58">
-        <v>-450.6059048077356</v>
+        <v>-466.590549893588</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09990759304827562</v>
+        <v>0.1011659091656774</v>
       </c>
       <c r="T58">
-        <v>1.249597991877035</v>
+        <v>1.27865841029278</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.08884020116636018</v>
+        <v>0.08728160114589772</v>
       </c>
       <c r="W58">
-        <v>0.1829608876057949</v>
+        <v>0.1832738544899037</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3443418649858921</v>
+        <v>0.3383007796352625</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1479674380004864</v>
+        <v>0.1495174380004864</v>
       </c>
       <c r="C59">
-        <v>-3561.738318729057</v>
+        <v>-3703.598734406152</v>
       </c>
       <c r="D59">
-        <v>2313.655688889981</v>
+        <v>2279.079378609712</v>
       </c>
       <c r="E59">
-        <v>4162.483467936516</v>
+        <v>4269.767573333342</v>
       </c>
       <c r="F59">
-        <v>6115.194007619038</v>
+        <v>6222.478113015864</v>
       </c>
       <c r="G59">
         <v>239.8</v>
@@ -6131,37 +6131,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M59">
-        <v>1227.930956729903</v>
+        <v>1249.473605093586</v>
       </c>
       <c r="N59">
-        <v>-812.520956729903</v>
+        <v>-834.0636050935857</v>
       </c>
       <c r="O59">
-        <v>-209.630406836315</v>
+        <v>-215.1884101141451</v>
       </c>
       <c r="P59">
-        <v>-602.8905498935881</v>
+        <v>-618.8751949794406</v>
       </c>
       <c r="Q59">
-        <v>-466.590549893588</v>
+        <v>-482.5751949794406</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1011659091656774</v>
+        <v>0.1024841450981935</v>
       </c>
       <c r="T59">
-        <v>1.27865841029278</v>
+        <v>1.309102658156894</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.08728160114589772</v>
+        <v>0.08577674595372706</v>
       </c>
       <c r="W59">
-        <v>0.1832738544899037</v>
+        <v>0.1835760294124916</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3383007796352625</v>
+        <v>0.3324680075725854</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1495174380004864</v>
+        <v>0.1510674380004864</v>
       </c>
       <c r="C60">
-        <v>-3703.59873440615</v>
+        <v>-3844.440919147785</v>
       </c>
       <c r="D60">
-        <v>2279.079378609712</v>
+        <v>2245.521299264903</v>
       </c>
       <c r="E60">
-        <v>4269.76757333334</v>
+        <v>4377.051678730166</v>
       </c>
       <c r="F60">
-        <v>6222.478113015862</v>
+        <v>6329.762218412688</v>
       </c>
       <c r="G60">
         <v>239.8</v>
@@ -6213,37 +6213,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M60">
-        <v>1249.473605093585</v>
+        <v>1271.016253457268</v>
       </c>
       <c r="N60">
-        <v>-834.0636050935852</v>
+        <v>-855.6062534572679</v>
       </c>
       <c r="O60">
-        <v>-215.188410114145</v>
+        <v>-220.7464133919751</v>
       </c>
       <c r="P60">
-        <v>-618.8751949794403</v>
+        <v>-634.8598400652928</v>
       </c>
       <c r="Q60">
-        <v>-482.5751949794403</v>
+        <v>-498.5598400652928</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1024841450981935</v>
+        <v>0.1038666852225397</v>
       </c>
       <c r="T60">
-        <v>1.309102658156893</v>
+        <v>1.341031991282671</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.08577674595372708</v>
+        <v>0.084322902801969</v>
       </c>
       <c r="W60">
-        <v>0.1835760294124916</v>
+        <v>0.1838679611173646</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6251,7 +6251,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3324680075725855</v>
+        <v>0.326832956596779</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1510674380004864</v>
+        <v>0.1526174380004864</v>
       </c>
       <c r="C61">
-        <v>-3844.440919147785</v>
+        <v>-3984.309198805041</v>
       </c>
       <c r="D61">
-        <v>2245.521299264903</v>
+        <v>2212.937125004472</v>
       </c>
       <c r="E61">
-        <v>4377.051678730166</v>
+        <v>4484.335784126991</v>
       </c>
       <c r="F61">
-        <v>6329.762218412688</v>
+        <v>6437.046323809513</v>
       </c>
       <c r="G61">
         <v>239.8</v>
@@ -6295,37 +6295,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M61">
-        <v>1271.016253457268</v>
+        <v>1292.55890182095</v>
       </c>
       <c r="N61">
-        <v>-855.6062534572679</v>
+        <v>-877.1489018209504</v>
       </c>
       <c r="O61">
-        <v>-220.7464133919751</v>
+        <v>-226.3044166698052</v>
       </c>
       <c r="P61">
-        <v>-634.8598400652928</v>
+        <v>-650.8444851511451</v>
       </c>
       <c r="Q61">
-        <v>-498.5598400652928</v>
+        <v>-514.5444851511452</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1038666852225397</v>
+        <v>0.1053183523531032</v>
       </c>
       <c r="T61">
-        <v>1.341031991282671</v>
+        <v>1.374557791064738</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.084322902801969</v>
+        <v>0.08291752108860284</v>
       </c>
       <c r="W61">
-        <v>0.1838679611173646</v>
+        <v>0.1841501617654085</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.326832956596779</v>
+        <v>0.3213857406534993</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1526174380004864</v>
+        <v>0.1541674380004864</v>
       </c>
       <c r="C62">
-        <v>-3984.309198805041</v>
+        <v>-4123.245363224813</v>
       </c>
       <c r="D62">
-        <v>2212.937125004472</v>
+        <v>2181.285065981525</v>
       </c>
       <c r="E62">
-        <v>4484.335784126991</v>
+        <v>4591.619889523816</v>
       </c>
       <c r="F62">
-        <v>6437.046323809513</v>
+        <v>6544.330429206338</v>
       </c>
       <c r="G62">
         <v>239.8</v>
@@ -6377,37 +6377,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M62">
-        <v>1292.55890182095</v>
+        <v>1314.101550184633</v>
       </c>
       <c r="N62">
-        <v>-877.1489018209504</v>
+        <v>-898.6915501846329</v>
       </c>
       <c r="O62">
-        <v>-226.3044166698052</v>
+        <v>-231.8624199476353</v>
       </c>
       <c r="P62">
-        <v>-650.8444851511451</v>
+        <v>-666.8291302369976</v>
       </c>
       <c r="Q62">
-        <v>-514.5444851511452</v>
+        <v>-530.5291302369976</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1053183523531032</v>
+        <v>0.1068444639519007</v>
       </c>
       <c r="T62">
-        <v>1.374557791064738</v>
+        <v>1.409802862630501</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.08291752108860284</v>
+        <v>0.08155821746419953</v>
       </c>
       <c r="W62">
-        <v>0.1841501617654085</v>
+        <v>0.1844231099331887</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3213857406534993</v>
+        <v>0.3161171219542617</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1541674380004864</v>
+        <v>0.1557174380004864</v>
       </c>
       <c r="C63">
-        <v>-4123.245363224813</v>
+        <v>-4261.288845057035</v>
       </c>
       <c r="D63">
-        <v>2181.285065981525</v>
+        <v>2150.525689546128</v>
       </c>
       <c r="E63">
-        <v>4591.619889523816</v>
+        <v>4698.903994920642</v>
       </c>
       <c r="F63">
-        <v>6544.330429206338</v>
+        <v>6651.614534603164</v>
       </c>
       <c r="G63">
         <v>239.8</v>
@@ -6459,37 +6459,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M63">
-        <v>1314.101550184633</v>
+        <v>1335.644198548315</v>
       </c>
       <c r="N63">
-        <v>-898.6915501846329</v>
+        <v>-920.2341985483154</v>
       </c>
       <c r="O63">
-        <v>-231.8624199476353</v>
+        <v>-237.4204232254654</v>
       </c>
       <c r="P63">
-        <v>-666.8291302369976</v>
+        <v>-682.81377532285</v>
       </c>
       <c r="Q63">
-        <v>-530.5291302369976</v>
+        <v>-546.5137753228501</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1068444639519007</v>
+        <v>0.1084508972137928</v>
       </c>
       <c r="T63">
-        <v>1.409802862630501</v>
+        <v>1.446902937962882</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.08155821746419953</v>
+        <v>0.0802427623438092</v>
       </c>
       <c r="W63">
-        <v>0.1844231099331887</v>
+        <v>0.1846872533213631</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3161171219542617</v>
+        <v>0.3110184586969349</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1557174380004864</v>
+        <v>0.1572674380004864</v>
       </c>
       <c r="C64">
-        <v>-4261.288845057035</v>
+        <v>-4398.476883643587</v>
       </c>
       <c r="D64">
-        <v>2150.525689546128</v>
+        <v>2120.621756356401</v>
       </c>
       <c r="E64">
-        <v>4698.903994920642</v>
+        <v>4806.188100317467</v>
       </c>
       <c r="F64">
-        <v>6651.614534603164</v>
+        <v>6758.898639999989</v>
       </c>
       <c r="G64">
         <v>239.8</v>
@@ -6541,37 +6541,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M64">
-        <v>1335.644198548315</v>
+        <v>1357.186846911998</v>
       </c>
       <c r="N64">
-        <v>-920.2341985483154</v>
+        <v>-941.7768469119978</v>
       </c>
       <c r="O64">
-        <v>-237.4204232254654</v>
+        <v>-242.9784265032955</v>
       </c>
       <c r="P64">
-        <v>-682.81377532285</v>
+        <v>-698.7984204087024</v>
       </c>
       <c r="Q64">
-        <v>-546.5137753228501</v>
+        <v>-562.4984204087025</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1084508972137928</v>
+        <v>0.1101441647060575</v>
       </c>
       <c r="T64">
-        <v>1.446902937962882</v>
+        <v>1.48600842277269</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.0802427623438092</v>
+        <v>0.07896906770343129</v>
       </c>
       <c r="W64">
-        <v>0.1846872533213631</v>
+        <v>0.184943011205151</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3110184586969349</v>
+        <v>0.3060816577652375</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1572674380004864</v>
+        <v>0.1588174380004864</v>
       </c>
       <c r="C65">
-        <v>-4398.476883643587</v>
+        <v>-4534.844675421077</v>
       </c>
       <c r="D65">
-        <v>2120.621756356401</v>
+        <v>2091.538069975737</v>
       </c>
       <c r="E65">
-        <v>4806.188100317467</v>
+        <v>4913.472205714293</v>
       </c>
       <c r="F65">
-        <v>6758.898639999989</v>
+        <v>6866.182745396814</v>
       </c>
       <c r="G65">
         <v>239.8</v>
@@ -6623,37 +6623,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M65">
-        <v>1357.186846911998</v>
+        <v>1378.72949527568</v>
       </c>
       <c r="N65">
-        <v>-941.7768469119978</v>
+        <v>-963.3194952756805</v>
       </c>
       <c r="O65">
-        <v>-242.9784265032955</v>
+        <v>-248.5364297811256</v>
       </c>
       <c r="P65">
-        <v>-698.7984204087024</v>
+        <v>-714.783065494555</v>
       </c>
       <c r="Q65">
-        <v>-562.4984204087025</v>
+        <v>-578.4830654945549</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1101441647060575</v>
+        <v>0.1119315026145591</v>
       </c>
       <c r="T65">
-        <v>1.48600842277269</v>
+        <v>1.527286434516375</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.07896906770343129</v>
+        <v>0.07773517602056516</v>
       </c>
       <c r="W65">
-        <v>0.184943011205151</v>
+        <v>0.1851907766550705</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.3060816577652375</v>
+        <v>0.3012991318626557</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1588174380004864</v>
+        <v>0.1603674380004864</v>
       </c>
       <c r="C66">
-        <v>-4534.844675421077</v>
+        <v>-4670.425512114702</v>
       </c>
       <c r="D66">
-        <v>2091.538069975737</v>
+        <v>2063.241338678938</v>
       </c>
       <c r="E66">
-        <v>4913.472205714293</v>
+        <v>5020.756311111118</v>
       </c>
       <c r="F66">
-        <v>6866.182745396814</v>
+        <v>6973.466850793639</v>
       </c>
       <c r="G66">
         <v>239.8</v>
@@ -6705,37 +6705,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M66">
-        <v>1378.72949527568</v>
+        <v>1400.272143639363</v>
       </c>
       <c r="N66">
-        <v>-963.3194952756805</v>
+        <v>-984.862143639363</v>
       </c>
       <c r="O66">
-        <v>-248.5364297811256</v>
+        <v>-254.0944330589557</v>
       </c>
       <c r="P66">
-        <v>-714.783065494555</v>
+        <v>-730.7677105804073</v>
       </c>
       <c r="Q66">
-        <v>-578.4830654945549</v>
+        <v>-594.4677105804074</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1119315026145591</v>
+        <v>0.1138209741178322</v>
       </c>
       <c r="T66">
-        <v>1.527286434516375</v>
+        <v>1.570923189788272</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.07773517602056516</v>
+        <v>0.07653925023563339</v>
       </c>
       <c r="W66">
-        <v>0.1851907766550705</v>
+        <v>0.1854309185526848</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3012991318626557</v>
+        <v>0.2966637606032302</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1603674380004864</v>
+        <v>0.1619174380004864</v>
       </c>
       <c r="C67">
-        <v>-4670.425512114702</v>
+        <v>-4805.250907863962</v>
       </c>
       <c r="D67">
-        <v>2063.241338678938</v>
+        <v>2035.700048326502</v>
       </c>
       <c r="E67">
-        <v>5020.756311111118</v>
+        <v>5128.040416507943</v>
       </c>
       <c r="F67">
-        <v>6973.466850793639</v>
+        <v>7080.750956190464</v>
       </c>
       <c r="G67">
         <v>239.8</v>
@@ -6787,37 +6787,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M67">
-        <v>1400.272143639363</v>
+        <v>1421.814792003045</v>
       </c>
       <c r="N67">
-        <v>-984.862143639363</v>
+        <v>-1006.404792003045</v>
       </c>
       <c r="O67">
-        <v>-254.0944330589557</v>
+        <v>-259.6524363367857</v>
       </c>
       <c r="P67">
-        <v>-730.7677105804073</v>
+        <v>-746.7523556662597</v>
       </c>
       <c r="Q67">
-        <v>-594.4677105804074</v>
+        <v>-610.4523556662598</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1138209741178322</v>
+        <v>0.1158215910036508</v>
       </c>
       <c r="T67">
-        <v>1.570923189788272</v>
+        <v>1.617126813017339</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.07653925023563339</v>
+        <v>0.07537956462600258</v>
       </c>
       <c r="W67">
-        <v>0.1854309185526848</v>
+        <v>0.1856637834230987</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2966637606032302</v>
+        <v>0.2921688551395448</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1619174380004864</v>
+        <v>0.1634674380004864</v>
       </c>
       <c r="C68">
-        <v>-4805.250907863962</v>
+        <v>-4939.350716300852</v>
       </c>
       <c r="D68">
-        <v>2035.700048326502</v>
+        <v>2008.884345286439</v>
       </c>
       <c r="E68">
-        <v>5128.040416507943</v>
+        <v>5235.324521904769</v>
       </c>
       <c r="F68">
-        <v>7080.750956190464</v>
+        <v>7188.03506158729</v>
       </c>
       <c r="G68">
         <v>239.8</v>
@@ -6869,37 +6869,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M68">
-        <v>1421.814792003045</v>
+        <v>1443.357440366728</v>
       </c>
       <c r="N68">
-        <v>-1006.404792003045</v>
+        <v>-1027.947440366728</v>
       </c>
       <c r="O68">
-        <v>-259.6524363367857</v>
+        <v>-265.2104396146159</v>
       </c>
       <c r="P68">
-        <v>-746.7523556662597</v>
+        <v>-762.7370007521123</v>
       </c>
       <c r="Q68">
-        <v>-610.4523556662598</v>
+        <v>-626.4370007521122</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1158215910036508</v>
+        <v>0.1179434573977008</v>
       </c>
       <c r="T68">
-        <v>1.617126813017339</v>
+        <v>1.666130655836046</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.07537956462600258</v>
+        <v>0.07425449649725627</v>
       </c>
       <c r="W68">
-        <v>0.1856637834230987</v>
+        <v>0.185889697103351</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2921688551395448</v>
+        <v>0.2878081259583576</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1634674380004864</v>
+        <v>0.1650174380004864</v>
       </c>
       <c r="C69">
-        <v>-4939.350716300852</v>
+        <v>-5072.753238494901</v>
       </c>
       <c r="D69">
-        <v>2008.884345286439</v>
+        <v>1982.765928489215</v>
       </c>
       <c r="E69">
-        <v>5235.324521904769</v>
+        <v>5342.608627301594</v>
       </c>
       <c r="F69">
-        <v>7188.03506158729</v>
+        <v>7295.319166984115</v>
       </c>
       <c r="G69">
         <v>239.8</v>
@@ -6951,37 +6951,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M69">
-        <v>1443.357440366728</v>
+        <v>1464.900088730411</v>
       </c>
       <c r="N69">
-        <v>-1027.947440366728</v>
+        <v>-1049.490088730411</v>
       </c>
       <c r="O69">
-        <v>-265.2104396146159</v>
+        <v>-270.7684428924459</v>
       </c>
       <c r="P69">
-        <v>-762.7370007521123</v>
+        <v>-778.7216458379647</v>
       </c>
       <c r="Q69">
-        <v>-626.4370007521122</v>
+        <v>-642.4216458379647</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1179434573977008</v>
+        <v>0.120197940441379</v>
       </c>
       <c r="T69">
-        <v>1.666130655836046</v>
+        <v>1.718197238830923</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.07425449649725627</v>
+        <v>0.07316251860759074</v>
       </c>
       <c r="W69">
-        <v>0.185889697103351</v>
+        <v>0.1861089662635958</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2878081259583576</v>
+        <v>0.2835756535177935</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1650174380004864</v>
+        <v>0.1665674380004864</v>
       </c>
       <c r="C70">
-        <v>-5072.753238494901</v>
+        <v>-5205.485322585668</v>
       </c>
       <c r="D70">
-        <v>1982.765928489215</v>
+        <v>1957.317949795273</v>
       </c>
       <c r="E70">
-        <v>5342.608627301594</v>
+        <v>5449.892732698419</v>
       </c>
       <c r="F70">
-        <v>7295.319166984115</v>
+        <v>7402.60327238094</v>
       </c>
       <c r="G70">
         <v>239.8</v>
@@ -7033,37 +7033,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M70">
-        <v>1464.900088730411</v>
+        <v>1486.442737094093</v>
       </c>
       <c r="N70">
-        <v>-1049.490088730411</v>
+        <v>-1071.032737094093</v>
       </c>
       <c r="O70">
-        <v>-270.7684428924459</v>
+        <v>-276.326446170276</v>
       </c>
       <c r="P70">
-        <v>-778.7216458379647</v>
+        <v>-794.7062909238169</v>
       </c>
       <c r="Q70">
-        <v>-642.4216458379647</v>
+        <v>-658.4062909238169</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.120197940441379</v>
+        <v>0.1225978740040041</v>
       </c>
       <c r="T70">
-        <v>1.718197238830923</v>
+        <v>1.773622956212565</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.07316251860759074</v>
+        <v>0.072102192250959</v>
       </c>
       <c r="W70">
-        <v>0.1861089662635958</v>
+        <v>0.1863218797960074</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2835756535177935</v>
+        <v>0.2794658614378255</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1665674380004864</v>
+        <v>0.1681174380004864</v>
       </c>
       <c r="C71">
-        <v>-5205.485322585668</v>
+        <v>-5337.572455839982</v>
       </c>
       <c r="D71">
-        <v>1957.317949795273</v>
+        <v>1932.514921937784</v>
       </c>
       <c r="E71">
-        <v>5449.892732698419</v>
+        <v>5557.176838095244</v>
       </c>
       <c r="F71">
-        <v>7402.60327238094</v>
+        <v>7509.887377777766</v>
       </c>
       <c r="G71">
         <v>239.8</v>
@@ -7115,37 +7115,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M71">
-        <v>1486.442737094093</v>
+        <v>1507.985385457775</v>
       </c>
       <c r="N71">
-        <v>-1071.032737094093</v>
+        <v>-1092.575385457776</v>
       </c>
       <c r="O71">
-        <v>-276.326446170276</v>
+        <v>-281.8844494481061</v>
       </c>
       <c r="P71">
-        <v>-794.7062909238169</v>
+        <v>-810.6909360096695</v>
       </c>
       <c r="Q71">
-        <v>-658.4062909238169</v>
+        <v>-674.3909360096695</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1225978740040041</v>
+        <v>0.1251578031374709</v>
       </c>
       <c r="T71">
-        <v>1.773622956212565</v>
+        <v>1.832743721419651</v>
       </c>
       <c r="U71">
         <v>0.2008</v>
       </c>
       <c r="V71">
-        <v>0.072102192250959</v>
+        <v>0.07107216093308814</v>
       </c>
       <c r="W71">
-        <v>0.1863218797960074</v>
+        <v>0.1865287100846359</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2794658614378255</v>
+        <v>0.2754734919887137</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1681174380004864</v>
+        <v>0.1696674380004864</v>
       </c>
       <c r="C72">
-        <v>-5337.572455839982</v>
+        <v>-5469.038849797516</v>
       </c>
       <c r="D72">
-        <v>1932.514921937784</v>
+        <v>1908.332633377074</v>
       </c>
       <c r="E72">
-        <v>5557.176838095244</v>
+        <v>5664.460943492069</v>
       </c>
       <c r="F72">
-        <v>7509.887377777766</v>
+        <v>7617.171483174591</v>
       </c>
       <c r="G72">
         <v>239.8</v>
@@ -7197,37 +7197,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M72">
-        <v>1507.985385457775</v>
+        <v>1529.528033821458</v>
       </c>
       <c r="N72">
-        <v>-1092.575385457776</v>
+        <v>-1114.118033821458</v>
       </c>
       <c r="O72">
-        <v>-281.8844494481061</v>
+        <v>-287.4424527259362</v>
       </c>
       <c r="P72">
-        <v>-810.6909360096695</v>
+        <v>-826.6755810955219</v>
       </c>
       <c r="Q72">
-        <v>-674.3909360096695</v>
+        <v>-690.375581095522</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1251578031374709</v>
+        <v>0.1278942791077285</v>
       </c>
       <c r="T72">
-        <v>1.832743721419651</v>
+        <v>1.895941780778949</v>
       </c>
       <c r="U72">
         <v>0.2008</v>
       </c>
       <c r="V72">
-        <v>0.07107216093308814</v>
+        <v>0.07007114458191789</v>
       </c>
       <c r="W72">
-        <v>0.1865287100846359</v>
+        <v>0.1867297141679509</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2754734919887137</v>
+        <v>0.2715935836508445</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1696674380004864</v>
+        <v>0.1712174380004864</v>
       </c>
       <c r="C73">
-        <v>-5469.038849797516</v>
+        <v>-5599.907519102615</v>
       </c>
       <c r="D73">
-        <v>1908.332633377074</v>
+        <v>1884.748069468801</v>
       </c>
       <c r="E73">
-        <v>5664.460943492069</v>
+        <v>5771.745048888894</v>
       </c>
       <c r="F73">
-        <v>7617.17148317459</v>
+        <v>7724.455588571415</v>
       </c>
       <c r="G73">
         <v>239.8</v>
@@ -7279,37 +7279,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M73">
-        <v>1529.528033821458</v>
+        <v>1551.07068218514</v>
       </c>
       <c r="N73">
-        <v>-1114.118033821458</v>
+        <v>-1135.66068218514</v>
       </c>
       <c r="O73">
-        <v>-287.4424527259361</v>
+        <v>-293.0004560037662</v>
       </c>
       <c r="P73">
-        <v>-826.6755810955217</v>
+        <v>-842.6602261813741</v>
       </c>
       <c r="Q73">
-        <v>-690.3755810955217</v>
+        <v>-706.3602261813742</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1278942791077285</v>
+        <v>0.1308262176472902</v>
       </c>
       <c r="T73">
-        <v>1.895941780778949</v>
+        <v>1.96365398723534</v>
       </c>
       <c r="U73">
         <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.0700711445819179</v>
+        <v>0.06909793424050237</v>
       </c>
       <c r="W73">
-        <v>0.1867297141679509</v>
+        <v>0.1869251348045071</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2715935836508445</v>
+        <v>0.2678214505445828</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1712174380004864</v>
+        <v>0.1727674380004864</v>
       </c>
       <c r="C74">
-        <v>-5599.907519102615</v>
+        <v>-5730.200354561909</v>
       </c>
       <c r="D74">
-        <v>1884.748069468801</v>
+        <v>1861.739339406331</v>
       </c>
       <c r="E74">
-        <v>5771.745048888894</v>
+        <v>5879.029154285719</v>
       </c>
       <c r="F74">
-        <v>7724.455588571415</v>
+        <v>7831.73969396824</v>
       </c>
       <c r="G74">
         <v>239.8</v>
@@ -7361,37 +7361,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M74">
-        <v>1551.07068218514</v>
+        <v>1572.613330548823</v>
       </c>
       <c r="N74">
-        <v>-1135.66068218514</v>
+        <v>-1157.203330548823</v>
       </c>
       <c r="O74">
-        <v>-293.0004560037662</v>
+        <v>-298.5584592815963</v>
       </c>
       <c r="P74">
-        <v>-842.6602261813741</v>
+        <v>-858.6448712672266</v>
       </c>
       <c r="Q74">
-        <v>-706.3602261813742</v>
+        <v>-722.3448712672266</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1308262176472902</v>
+        <v>0.1339753368194121</v>
       </c>
       <c r="T74">
-        <v>1.96365398723534</v>
+        <v>2.0363819126885</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.06909793424050237</v>
+        <v>0.06815138719611194</v>
       </c>
       <c r="W74">
-        <v>0.1869251348045071</v>
+        <v>0.1871152014510207</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2678214505445828</v>
+        <v>0.2641526635508215</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1727674380004864</v>
+        <v>0.1743174380004864</v>
       </c>
       <c r="C75">
-        <v>-5730.200354561909</v>
+        <v>-5859.938190915222</v>
       </c>
       <c r="D75">
-        <v>1861.739339406331</v>
+        <v>1839.285608449844</v>
       </c>
       <c r="E75">
-        <v>5879.029154285719</v>
+        <v>5986.313259682544</v>
       </c>
       <c r="F75">
-        <v>7831.73969396824</v>
+        <v>7939.023799365066</v>
       </c>
       <c r="G75">
         <v>239.8</v>
@@ -7443,37 +7443,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M75">
-        <v>1572.613330548823</v>
+        <v>1594.155978912505</v>
       </c>
       <c r="N75">
-        <v>-1157.203330548823</v>
+        <v>-1178.745978912506</v>
       </c>
       <c r="O75">
-        <v>-298.5584592815963</v>
+        <v>-304.1164625594265</v>
       </c>
       <c r="P75">
-        <v>-858.6448712672266</v>
+        <v>-874.629516353079</v>
       </c>
       <c r="Q75">
-        <v>-722.3448712672266</v>
+        <v>-738.329516353079</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1339753368194121</v>
+        <v>0.137366695927851</v>
       </c>
       <c r="T75">
-        <v>2.0363819126885</v>
+        <v>2.11470429394575</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.06815138719611194</v>
+        <v>0.06723042250427258</v>
       </c>
       <c r="W75">
-        <v>0.1871152014510207</v>
+        <v>0.1873001311611421</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2641526635508215</v>
+        <v>0.2605830329622968</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1743174380004864</v>
+        <v>0.1758674380004864</v>
       </c>
       <c r="C76">
-        <v>-5859.938190915222</v>
+        <v>-5989.140869760742</v>
       </c>
       <c r="D76">
-        <v>1839.285608449844</v>
+        <v>1817.367035001149</v>
       </c>
       <c r="E76">
-        <v>5986.313259682544</v>
+        <v>6093.597365079369</v>
       </c>
       <c r="F76">
-        <v>7939.023799365066</v>
+        <v>8046.307904761891</v>
       </c>
       <c r="G76">
         <v>239.8</v>
@@ -7525,37 +7525,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M76">
-        <v>1594.155978912505</v>
+        <v>1615.698627276188</v>
       </c>
       <c r="N76">
-        <v>-1178.745978912506</v>
+        <v>-1200.288627276188</v>
       </c>
       <c r="O76">
-        <v>-304.1164625594265</v>
+        <v>-309.6744658372565</v>
       </c>
       <c r="P76">
-        <v>-874.629516353079</v>
+        <v>-890.6141614389314</v>
       </c>
       <c r="Q76">
-        <v>-738.329516353079</v>
+        <v>-754.3141614389315</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.137366695927851</v>
+        <v>0.1410293637649651</v>
       </c>
       <c r="T76">
-        <v>2.11470429394575</v>
+        <v>2.199292465703581</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.06723042250427258</v>
+        <v>0.06633401687088226</v>
       </c>
       <c r="W76">
-        <v>0.1873001311611421</v>
+        <v>0.1874801294123269</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2605830329622968</v>
+        <v>0.2571085925227995</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1758674380004864</v>
+        <v>0.1774174380004864</v>
       </c>
       <c r="C77">
-        <v>-5989.140869760742</v>
+        <v>-6117.827298033973</v>
       </c>
       <c r="D77">
-        <v>1817.367035001149</v>
+        <v>1795.964712124743</v>
       </c>
       <c r="E77">
-        <v>6093.597365079369</v>
+        <v>6200.881470476194</v>
       </c>
       <c r="F77">
-        <v>8046.307904761891</v>
+        <v>8153.592010158716</v>
       </c>
       <c r="G77">
         <v>239.8</v>
@@ -7607,37 +7607,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M77">
-        <v>1615.698627276188</v>
+        <v>1637.24127563987</v>
       </c>
       <c r="N77">
-        <v>-1200.288627276188</v>
+        <v>-1221.83127563987</v>
       </c>
       <c r="O77">
-        <v>-309.6744658372565</v>
+        <v>-315.2324691150866</v>
       </c>
       <c r="P77">
-        <v>-890.6141614389314</v>
+        <v>-906.5988065247839</v>
       </c>
       <c r="Q77">
-        <v>-754.3141614389315</v>
+        <v>-770.2988065247839</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1410293637649651</v>
+        <v>0.1449972539218386</v>
       </c>
       <c r="T77">
-        <v>2.199292465703581</v>
+        <v>2.290929651774563</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.06633401687088226</v>
+        <v>0.06546120085942331</v>
       </c>
       <c r="W77">
-        <v>0.1874801294123269</v>
+        <v>0.1876553908674278</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2571085925227995</v>
+        <v>0.2537255847264469</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1774174380004864</v>
+        <v>0.1789674380004864</v>
       </c>
       <c r="C78">
-        <v>-6117.827298033973</v>
+        <v>-6246.015502402675</v>
       </c>
       <c r="D78">
-        <v>1795.964712124743</v>
+        <v>1775.060613152867</v>
       </c>
       <c r="E78">
-        <v>6200.881470476194</v>
+        <v>6308.16557587302</v>
       </c>
       <c r="F78">
-        <v>8153.592010158716</v>
+        <v>8260.876115555542</v>
       </c>
       <c r="G78">
         <v>239.8</v>
@@ -7689,37 +7689,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M78">
-        <v>1637.24127563987</v>
+        <v>1658.783924003553</v>
       </c>
       <c r="N78">
-        <v>-1221.83127563987</v>
+        <v>-1243.373924003553</v>
       </c>
       <c r="O78">
-        <v>-315.2324691150866</v>
+        <v>-320.7904723929167</v>
       </c>
       <c r="P78">
-        <v>-906.5988065247839</v>
+        <v>-922.5834516106364</v>
       </c>
       <c r="Q78">
-        <v>-770.2988065247839</v>
+        <v>-786.2834516106363</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1449972539218386</v>
+        <v>0.1493101780053968</v>
       </c>
       <c r="T78">
-        <v>2.290929651774563</v>
+        <v>2.39053528880824</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.06546120085942331</v>
+        <v>0.0646110553937165</v>
       </c>
       <c r="W78">
-        <v>0.1876553908674278</v>
+        <v>0.1878261000769417</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2537255847264469</v>
+        <v>0.250430447262467</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1789674380004864</v>
+        <v>0.1805174380004864</v>
       </c>
       <c r="C79">
-        <v>-6246.015502402675</v>
+        <v>-6373.722679906744</v>
       </c>
       <c r="D79">
-        <v>1775.060613152867</v>
+        <v>1754.637541045624</v>
       </c>
       <c r="E79">
-        <v>6308.16557587302</v>
+        <v>6415.449681269846</v>
       </c>
       <c r="F79">
-        <v>8260.876115555542</v>
+        <v>8368.160220952368</v>
       </c>
       <c r="G79">
         <v>239.8</v>
@@ -7771,37 +7771,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M79">
-        <v>1658.783924003553</v>
+        <v>1680.326572367235</v>
       </c>
       <c r="N79">
-        <v>-1243.373924003553</v>
+        <v>-1264.916572367236</v>
       </c>
       <c r="O79">
-        <v>-320.7904723929167</v>
+        <v>-326.3484756707468</v>
       </c>
       <c r="P79">
-        <v>-922.5834516106364</v>
+        <v>-938.5680966964889</v>
       </c>
       <c r="Q79">
-        <v>-786.2834516106363</v>
+        <v>-802.2680966964888</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1493101780053968</v>
+        <v>0.1540151860965512</v>
       </c>
       <c r="T79">
-        <v>2.39053528880824</v>
+        <v>2.49919598375407</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.0646110553937165</v>
+        <v>0.06378270852969449</v>
       </c>
       <c r="W79">
-        <v>0.1878261000769417</v>
+        <v>0.1879924321272373</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.250430447262467</v>
+        <v>0.2472198005026918</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1805174380004864</v>
+        <v>0.1820674380004864</v>
       </c>
       <c r="C80">
-        <v>-6373.722679906744</v>
+        <v>-6500.965245142015</v>
       </c>
       <c r="D80">
-        <v>1754.637541045624</v>
+        <v>1734.679081207177</v>
       </c>
       <c r="E80">
-        <v>6415.449681269846</v>
+        <v>6522.73378666667</v>
       </c>
       <c r="F80">
-        <v>8368.160220952368</v>
+        <v>8475.444326349192</v>
       </c>
       <c r="G80">
         <v>239.8</v>
@@ -7853,37 +7853,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M80">
-        <v>1680.326572367235</v>
+        <v>1701.869220730918</v>
       </c>
       <c r="N80">
-        <v>-1264.916572367236</v>
+        <v>-1286.459220730918</v>
       </c>
       <c r="O80">
-        <v>-326.3484756707468</v>
+        <v>-331.9064789485768</v>
       </c>
       <c r="P80">
-        <v>-938.5680966964889</v>
+        <v>-954.5527417823411</v>
       </c>
       <c r="Q80">
-        <v>-802.2680966964888</v>
+        <v>-818.252741782341</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1540151860965512</v>
+        <v>0.159168290196387</v>
       </c>
       <c r="T80">
-        <v>2.49919598375407</v>
+        <v>2.618205316313787</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.06378270852969449</v>
+        <v>0.06297533247235659</v>
       </c>
       <c r="W80">
-        <v>0.1879924321272373</v>
+        <v>0.1881545532395508</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2472198005026918</v>
+        <v>0.2440904359393666</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1820674380004864</v>
+        <v>0.1836174380004864</v>
       </c>
       <c r="C81">
-        <v>-6500.965245142015</v>
+        <v>-6627.758874260082</v>
       </c>
       <c r="D81">
-        <v>1734.679081207177</v>
+        <v>1715.169557485937</v>
       </c>
       <c r="E81">
-        <v>6522.73378666667</v>
+        <v>6630.017892063496</v>
       </c>
       <c r="F81">
-        <v>8475.444326349192</v>
+        <v>8582.728431746018</v>
       </c>
       <c r="G81">
         <v>239.8</v>
@@ -7935,37 +7935,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M81">
-        <v>1701.869220730918</v>
+        <v>1723.4118690946</v>
       </c>
       <c r="N81">
-        <v>-1286.459220730918</v>
+        <v>-1308.001869094601</v>
       </c>
       <c r="O81">
-        <v>-331.9064789485768</v>
+        <v>-337.464482226407</v>
       </c>
       <c r="P81">
-        <v>-954.5527417823411</v>
+        <v>-970.5373868681936</v>
       </c>
       <c r="Q81">
-        <v>-818.252741782341</v>
+        <v>-834.2373868681937</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.159168290196387</v>
+        <v>0.1648367047062063</v>
       </c>
       <c r="T81">
-        <v>2.618205316313787</v>
+        <v>2.749115582129476</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.06297533247235659</v>
+        <v>0.06218814081645213</v>
       </c>
       <c r="W81">
-        <v>0.1881545532395508</v>
+        <v>0.1883126213240564</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2440904359393666</v>
+        <v>0.2410393054901245</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1836174380004864</v>
+        <v>0.1851674380004864</v>
       </c>
       <c r="C82">
-        <v>-6627.758874260082</v>
+        <v>-6754.118546031988</v>
       </c>
       <c r="D82">
-        <v>1715.169557485937</v>
+        <v>1696.093991110856</v>
       </c>
       <c r="E82">
-        <v>6630.017892063496</v>
+        <v>6737.301997460322</v>
       </c>
       <c r="F82">
-        <v>8582.728431746018</v>
+        <v>8690.012537142844</v>
       </c>
       <c r="G82">
         <v>239.8</v>
@@ -8017,37 +8017,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M82">
-        <v>1723.4118690946</v>
+        <v>1744.954517458283</v>
       </c>
       <c r="N82">
-        <v>-1308.001869094601</v>
+        <v>-1329.544517458283</v>
       </c>
       <c r="O82">
-        <v>-337.464482226407</v>
+        <v>-343.0224855042371</v>
       </c>
       <c r="P82">
-        <v>-970.5373868681936</v>
+        <v>-986.5220319540463</v>
       </c>
       <c r="Q82">
-        <v>-834.2373868681937</v>
+        <v>-850.2220319540463</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1648367047062063</v>
+        <v>0.1711017944275856</v>
       </c>
       <c r="T82">
-        <v>2.749115582129476</v>
+        <v>2.893805875925765</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.06218814081645213</v>
+        <v>0.06142038599155766</v>
       </c>
       <c r="W82">
-        <v>0.1883126213240564</v>
+        <v>0.1884667864928952</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2410393054901245</v>
+        <v>0.2380635115951847</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1851674380004864</v>
+        <v>0.1867174380004864</v>
       </c>
       <c r="C83">
-        <v>-6754.118546031988</v>
+        <v>-6880.058580201891</v>
       </c>
       <c r="D83">
-        <v>1696.093991110856</v>
+        <v>1677.438062337777</v>
       </c>
       <c r="E83">
-        <v>6737.301997460322</v>
+        <v>6844.586102857146</v>
       </c>
       <c r="F83">
-        <v>8690.012537142844</v>
+        <v>8797.296642539668</v>
       </c>
       <c r="G83">
         <v>239.8</v>
@@ -8099,37 +8099,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M83">
-        <v>1744.954517458283</v>
+        <v>1766.497165821965</v>
       </c>
       <c r="N83">
-        <v>-1329.544517458283</v>
+        <v>-1351.087165821966</v>
       </c>
       <c r="O83">
-        <v>-343.0224855042371</v>
+        <v>-348.5804887820671</v>
       </c>
       <c r="P83">
-        <v>-986.5220319540463</v>
+        <v>-1002.506677039898</v>
       </c>
       <c r="Q83">
-        <v>-850.2220319540463</v>
+        <v>-866.2066770398985</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1711017944275856</v>
+        <v>0.1780630052291182</v>
       </c>
       <c r="T83">
-        <v>2.893805875925765</v>
+        <v>3.054572869032751</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.06142038599155766</v>
+        <v>0.06067135689409964</v>
       </c>
       <c r="W83">
-        <v>0.1884667864928952</v>
+        <v>0.1886171915356648</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2380635115951847</v>
+        <v>0.2351602980391458</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1867174380004864</v>
+        <v>0.1882674380004864</v>
       </c>
       <c r="C84">
-        <v>-6880.058580201891</v>
+        <v>-7005.592673337071</v>
       </c>
       <c r="D84">
-        <v>1677.438062337777</v>
+        <v>1659.188074599423</v>
       </c>
       <c r="E84">
-        <v>6844.586102857146</v>
+        <v>6951.870208253972</v>
       </c>
       <c r="F84">
-        <v>8797.296642539668</v>
+        <v>8904.580747936494</v>
       </c>
       <c r="G84">
         <v>239.8</v>
@@ -8181,37 +8181,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M84">
-        <v>1766.497165821965</v>
+        <v>1788.039814185648</v>
       </c>
       <c r="N84">
-        <v>-1351.087165821966</v>
+        <v>-1372.629814185648</v>
       </c>
       <c r="O84">
-        <v>-348.5804887820671</v>
+        <v>-354.1384920598973</v>
       </c>
       <c r="P84">
-        <v>-1002.506677039898</v>
+        <v>-1018.491322125751</v>
       </c>
       <c r="Q84">
-        <v>-866.2066770398985</v>
+        <v>-882.191322125751</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1780630052291182</v>
+        <v>0.1858431820073016</v>
       </c>
       <c r="T84">
-        <v>3.054572869032751</v>
+        <v>3.234253626034679</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.06067135689409964</v>
+        <v>0.05994037669055627</v>
       </c>
       <c r="W84">
-        <v>0.1886171915356648</v>
+        <v>0.1887639723605363</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2351602980391458</v>
+        <v>0.2323270414362646</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1882674380004864</v>
+        <v>0.1898174380004864</v>
       </c>
       <c r="C85">
-        <v>-7005.592673337071</v>
+        <v>-7130.733932362892</v>
       </c>
       <c r="D85">
-        <v>1659.188074599423</v>
+        <v>1641.330920970428</v>
       </c>
       <c r="E85">
-        <v>6951.870208253972</v>
+        <v>7059.154313650798</v>
       </c>
       <c r="F85">
-        <v>8904.580747936494</v>
+        <v>9011.86485333332</v>
       </c>
       <c r="G85">
         <v>239.8</v>
@@ -8263,37 +8263,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M85">
-        <v>1788.039814185648</v>
+        <v>1809.582462549331</v>
       </c>
       <c r="N85">
-        <v>-1372.629814185648</v>
+        <v>-1394.172462549331</v>
       </c>
       <c r="O85">
-        <v>-354.1384920598973</v>
+        <v>-359.6964953377274</v>
       </c>
       <c r="P85">
-        <v>-1018.491322125751</v>
+        <v>-1034.475967211604</v>
       </c>
       <c r="Q85">
-        <v>-882.191322125751</v>
+        <v>-898.1759672116036</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1858431820073016</v>
+        <v>0.194595880882758</v>
       </c>
       <c r="T85">
-        <v>3.234253626034679</v>
+        <v>3.436394477661846</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.05994037669055627</v>
+        <v>0.05922680077757345</v>
       </c>
       <c r="W85">
-        <v>0.1887639723605363</v>
+        <v>0.1889072584038632</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2323270414362646</v>
+        <v>0.229561243323928</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1898174380004864</v>
+        <v>0.1913674380004864</v>
       </c>
       <c r="C86">
-        <v>-7130.73393236289</v>
+        <v>-7255.494905955306</v>
       </c>
       <c r="D86">
-        <v>1641.330920970428</v>
+        <v>1623.854052774838</v>
       </c>
       <c r="E86">
-        <v>7059.154313650796</v>
+        <v>7166.438419047622</v>
       </c>
       <c r="F86">
-        <v>9011.864853333318</v>
+        <v>9119.148958730144</v>
       </c>
       <c r="G86">
         <v>239.8</v>
@@ -8345,37 +8345,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M86">
-        <v>1809.58246254933</v>
+        <v>1831.125110913013</v>
       </c>
       <c r="N86">
-        <v>-1394.17246254933</v>
+        <v>-1415.715110913013</v>
       </c>
       <c r="O86">
-        <v>-359.6964953377273</v>
+        <v>-365.2544986155574</v>
       </c>
       <c r="P86">
-        <v>-1034.475967211603</v>
+        <v>-1050.460612297456</v>
       </c>
       <c r="Q86">
-        <v>-898.1759672116032</v>
+        <v>-914.1606122974558</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1945958808827579</v>
+        <v>0.2045156062749418</v>
       </c>
       <c r="T86">
-        <v>3.436394477661844</v>
+        <v>3.665487442839301</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.05922680077757346</v>
+        <v>0.0585300148860726</v>
       </c>
       <c r="W86">
-        <v>0.1889072584038632</v>
+        <v>0.1890471730108766</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2295612433239281</v>
+        <v>0.2268605228142349</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1913674380004864</v>
+        <v>0.1929174380004864</v>
       </c>
       <c r="C87">
-        <v>-7255.494905955306</v>
+        <v>-7379.88761394887</v>
       </c>
       <c r="D87">
-        <v>1623.854052774838</v>
+        <v>1606.745450178098</v>
       </c>
       <c r="E87">
-        <v>7166.438419047622</v>
+        <v>7273.722524444446</v>
       </c>
       <c r="F87">
-        <v>9119.148958730144</v>
+        <v>9226.433064126968</v>
       </c>
       <c r="G87">
         <v>239.8</v>
@@ -8427,37 +8427,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M87">
-        <v>1831.125110913013</v>
+        <v>1852.667759276695</v>
       </c>
       <c r="N87">
-        <v>-1415.715110913013</v>
+        <v>-1437.257759276695</v>
       </c>
       <c r="O87">
-        <v>-365.2544986155574</v>
+        <v>-370.8125018933874</v>
       </c>
       <c r="P87">
-        <v>-1050.460612297456</v>
+        <v>-1066.445257383308</v>
       </c>
       <c r="Q87">
-        <v>-914.1606122974558</v>
+        <v>-930.145257383308</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2045156062749418</v>
+        <v>0.2158524352945804</v>
       </c>
       <c r="T87">
-        <v>3.665487442839301</v>
+        <v>3.927307974470679</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.0585300148860726</v>
+        <v>0.05784943331762989</v>
       </c>
       <c r="W87">
-        <v>0.1890471730108766</v>
+        <v>0.1891838337898199</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8465,7 +8465,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2268605228142349</v>
+        <v>0.2242226097582554</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1929174380004864</v>
+        <v>0.1944674380004864</v>
       </c>
       <c r="C88">
-        <v>-7379.88761394887</v>
+        <v>-7503.923574905137</v>
       </c>
       <c r="D88">
-        <v>1606.745450178098</v>
+        <v>1589.993594618657</v>
       </c>
       <c r="E88">
-        <v>7273.722524444446</v>
+        <v>7381.006629841272</v>
       </c>
       <c r="F88">
-        <v>9226.433064126968</v>
+        <v>9333.717169523794</v>
       </c>
       <c r="G88">
         <v>239.8</v>
@@ -8509,37 +8509,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M88">
-        <v>1852.667759276695</v>
+        <v>1874.210407640378</v>
       </c>
       <c r="N88">
-        <v>-1437.257759276695</v>
+        <v>-1458.800407640378</v>
       </c>
       <c r="O88">
-        <v>-370.8125018933874</v>
+        <v>-376.3705051712176</v>
       </c>
       <c r="P88">
-        <v>-1066.445257383308</v>
+        <v>-1082.42990246916</v>
       </c>
       <c r="Q88">
-        <v>-930.145257383308</v>
+        <v>-946.1299024691605</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2158524352945804</v>
+        <v>0.228933391855702</v>
       </c>
       <c r="T88">
-        <v>3.927307974470679</v>
+        <v>4.2294085878915</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.05784943331762989</v>
+        <v>0.05718449730248472</v>
       </c>
       <c r="W88">
-        <v>0.1891838337898199</v>
+        <v>0.1893173529416611</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2242226097582554</v>
+        <v>0.2216453383817237</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1944674380004864</v>
+        <v>0.1960174380004864</v>
       </c>
       <c r="C89">
-        <v>-7503.923574905137</v>
+        <v>-7627.613831974254</v>
       </c>
       <c r="D89">
-        <v>1589.993594618657</v>
+        <v>1573.587442946366</v>
       </c>
       <c r="E89">
-        <v>7381.006629841272</v>
+        <v>7488.290735238098</v>
       </c>
       <c r="F89">
-        <v>9333.717169523794</v>
+        <v>9441.00127492062</v>
       </c>
       <c r="G89">
         <v>239.8</v>
@@ -8591,37 +8591,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M89">
-        <v>1874.210407640378</v>
+        <v>1895.75305600406</v>
       </c>
       <c r="N89">
-        <v>-1458.800407640378</v>
+        <v>-1480.343056004061</v>
       </c>
       <c r="O89">
-        <v>-376.3705051712176</v>
+        <v>-381.9285084490476</v>
       </c>
       <c r="P89">
-        <v>-1082.42990246916</v>
+        <v>-1098.414547555013</v>
       </c>
       <c r="Q89">
-        <v>-946.1299024691605</v>
+        <v>-962.1145475550131</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.228933391855702</v>
+        <v>0.2441945078436772</v>
       </c>
       <c r="T89">
-        <v>4.2294085878915</v>
+        <v>4.581859303549127</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.05718449730248472</v>
+        <v>0.05653467346950194</v>
       </c>
       <c r="W89">
-        <v>0.1893173529416611</v>
+        <v>0.189447837567324</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2216453383817237</v>
+        <v>0.2191266413546586</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1960174380004864</v>
+        <v>0.1975674380004864</v>
       </c>
       <c r="C90">
-        <v>-7627.613831974254</v>
+        <v>-7750.968977171848</v>
       </c>
       <c r="D90">
-        <v>1573.587442946366</v>
+        <v>1557.516403145596</v>
       </c>
       <c r="E90">
-        <v>7488.290735238098</v>
+        <v>7595.574840634922</v>
       </c>
       <c r="F90">
-        <v>9441.00127492062</v>
+        <v>9548.285380317444</v>
       </c>
       <c r="G90">
         <v>239.8</v>
@@ -8673,37 +8673,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M90">
-        <v>1895.75305600406</v>
+        <v>1917.295704367743</v>
       </c>
       <c r="N90">
-        <v>-1480.343056004061</v>
+        <v>-1501.885704367743</v>
       </c>
       <c r="O90">
-        <v>-381.9285084490476</v>
+        <v>-387.4865117268777</v>
       </c>
       <c r="P90">
-        <v>-1098.414547555013</v>
+        <v>-1114.399192640865</v>
       </c>
       <c r="Q90">
-        <v>-962.1145475550131</v>
+        <v>-978.0991926408653</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2441945078436772</v>
+        <v>0.2622303721931024</v>
       </c>
       <c r="T90">
-        <v>4.581859303549127</v>
+        <v>4.998391967508138</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.05653467346950194</v>
+        <v>0.05589945241928283</v>
       </c>
       <c r="W90">
-        <v>0.189447837567324</v>
+        <v>0.189575389954208</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2191266413546586</v>
+        <v>0.2166645442607861</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1975674380004864</v>
+        <v>0.1991174380004864</v>
       </c>
       <c r="C91">
-        <v>-7750.968977171848</v>
+        <v>-7873.999174183302</v>
       </c>
       <c r="D91">
-        <v>1557.516403145596</v>
+        <v>1541.770311530968</v>
       </c>
       <c r="E91">
-        <v>7595.574840634922</v>
+        <v>7702.858946031748</v>
       </c>
       <c r="F91">
-        <v>9548.285380317444</v>
+        <v>9655.56948571427</v>
       </c>
       <c r="G91">
         <v>239.8</v>
@@ -8755,37 +8755,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M91">
-        <v>1917.295704367743</v>
+        <v>1938.838352731425</v>
       </c>
       <c r="N91">
-        <v>-1501.885704367743</v>
+        <v>-1523.428352731426</v>
       </c>
       <c r="O91">
-        <v>-387.4865117268777</v>
+        <v>-393.0445150047078</v>
       </c>
       <c r="P91">
-        <v>-1114.399192640865</v>
+        <v>-1130.383837726718</v>
       </c>
       <c r="Q91">
-        <v>-978.0991926408653</v>
+        <v>-994.0838377267178</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2622303721931024</v>
+        <v>0.2838734094124127</v>
       </c>
       <c r="T91">
-        <v>4.998391967508138</v>
+        <v>5.498231164258953</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.05589945241928283</v>
+        <v>0.05527834739240189</v>
       </c>
       <c r="W91">
-        <v>0.189575389954208</v>
+        <v>0.1897001078436057</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2166645442607861</v>
+        <v>0.2142571604356662</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1991174380004864</v>
+        <v>0.2006674380004864</v>
       </c>
       <c r="C92">
-        <v>-7873.999174183302</v>
+        <v>-7996.714179798581</v>
       </c>
       <c r="D92">
-        <v>1541.770311530968</v>
+        <v>1526.339411312515</v>
       </c>
       <c r="E92">
-        <v>7702.858946031748</v>
+        <v>7810.143051428574</v>
       </c>
       <c r="F92">
-        <v>9655.56948571427</v>
+        <v>9762.853591111096</v>
       </c>
       <c r="G92">
         <v>239.8</v>
@@ -8837,37 +8837,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M92">
-        <v>1938.838352731425</v>
+        <v>1960.381001095108</v>
       </c>
       <c r="N92">
-        <v>-1523.428352731426</v>
+        <v>-1544.971001095108</v>
       </c>
       <c r="O92">
-        <v>-393.0445150047078</v>
+        <v>-398.6025182825379</v>
       </c>
       <c r="P92">
-        <v>-1130.383837726718</v>
+        <v>-1146.36848281257</v>
       </c>
       <c r="Q92">
-        <v>-994.0838377267178</v>
+        <v>-1010.06848281257</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2838734094124127</v>
+        <v>0.3103260104582363</v>
       </c>
       <c r="T92">
-        <v>5.498231164258953</v>
+        <v>6.109145738065503</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.05527834739240189</v>
+        <v>0.05467089302545242</v>
       </c>
       <c r="W92">
-        <v>0.1897001078436057</v>
+        <v>0.1898220846804891</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2142571604356662</v>
+        <v>0.2119026861451644</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2006674380004864</v>
+        <v>0.2022174380004864</v>
       </c>
       <c r="C93">
-        <v>-7996.714179798581</v>
+        <v>-8119.123364072653</v>
       </c>
       <c r="D93">
-        <v>1526.339411312515</v>
+        <v>1511.214332435266</v>
       </c>
       <c r="E93">
-        <v>7810.143051428574</v>
+        <v>7917.427156825398</v>
       </c>
       <c r="F93">
-        <v>9762.853591111096</v>
+        <v>9870.13769650792</v>
       </c>
       <c r="G93">
         <v>239.8</v>
@@ -8919,37 +8919,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M93">
-        <v>1960.381001095108</v>
+        <v>1981.92364945879</v>
       </c>
       <c r="N93">
-        <v>-1544.971001095108</v>
+        <v>-1566.51364945879</v>
       </c>
       <c r="O93">
-        <v>-398.6025182825379</v>
+        <v>-404.160521560368</v>
       </c>
       <c r="P93">
-        <v>-1146.36848281257</v>
+        <v>-1162.353127898423</v>
       </c>
       <c r="Q93">
-        <v>-1010.06848281257</v>
+        <v>-1026.053127898423</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3103260104582363</v>
+        <v>0.343391761765516</v>
       </c>
       <c r="T93">
-        <v>6.109145738065503</v>
+        <v>6.872788955323694</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.05467089302545242</v>
+        <v>0.05407664418821925</v>
       </c>
       <c r="W93">
-        <v>0.1898220846804891</v>
+        <v>0.1899414098470056</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2119026861451644</v>
+        <v>0.2095993960783692</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2022174380004864</v>
+        <v>0.2037674380004864</v>
       </c>
       <c r="C94">
-        <v>-8119.123364072653</v>
+        <v>-8241.235729298998</v>
       </c>
       <c r="D94">
-        <v>1511.214332435266</v>
+        <v>1496.386072605747</v>
       </c>
       <c r="E94">
-        <v>7917.427156825398</v>
+        <v>8024.711262222224</v>
       </c>
       <c r="F94">
-        <v>9870.13769650792</v>
+        <v>9977.421801904746</v>
       </c>
       <c r="G94">
         <v>239.8</v>
@@ -9001,37 +9001,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M94">
-        <v>1981.92364945879</v>
+        <v>2003.466297822473</v>
       </c>
       <c r="N94">
-        <v>-1566.51364945879</v>
+        <v>-1588.056297822473</v>
       </c>
       <c r="O94">
-        <v>-404.160521560368</v>
+        <v>-409.7185248381981</v>
       </c>
       <c r="P94">
-        <v>-1162.353127898423</v>
+        <v>-1178.337772984275</v>
       </c>
       <c r="Q94">
-        <v>-1026.053127898423</v>
+        <v>-1042.037772984275</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.343391761765516</v>
+        <v>0.3859048705891611</v>
       </c>
       <c r="T94">
-        <v>6.872788955323694</v>
+        <v>7.854615948941365</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.05407664418821925</v>
+        <v>0.0534951748958728</v>
       </c>
       <c r="W94">
-        <v>0.1899414098470056</v>
+        <v>0.1900581688809088</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2095993960783692</v>
+        <v>0.2073456391312899</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2037674380004864</v>
+        <v>0.2053174380004864</v>
       </c>
       <c r="C95">
-        <v>-8241.235729298998</v>
+        <v>-8363.059927876933</v>
       </c>
       <c r="D95">
-        <v>1496.386072605747</v>
+        <v>1481.845979424638</v>
       </c>
       <c r="E95">
-        <v>8024.711262222224</v>
+        <v>8131.99536761905</v>
       </c>
       <c r="F95">
-        <v>9977.421801904746</v>
+        <v>10084.70590730157</v>
       </c>
       <c r="G95">
         <v>239.8</v>
@@ -9083,37 +9083,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M95">
-        <v>2003.466297822473</v>
+        <v>2025.008946186156</v>
       </c>
       <c r="N95">
-        <v>-1588.056297822473</v>
+        <v>-1609.598946186156</v>
       </c>
       <c r="O95">
-        <v>-409.7185248381981</v>
+        <v>-415.2765281160283</v>
       </c>
       <c r="P95">
-        <v>-1178.337772984275</v>
+        <v>-1194.322418070128</v>
       </c>
       <c r="Q95">
-        <v>-1042.037772984275</v>
+        <v>-1058.022418070128</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3859048705891611</v>
+        <v>0.4425890156873548</v>
       </c>
       <c r="T95">
-        <v>7.854615948941365</v>
+        <v>9.163718607098263</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.0534951748958728</v>
+        <v>0.05292607729059755</v>
       </c>
       <c r="W95">
-        <v>0.1900581688809088</v>
+        <v>0.190172443680048</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2073456391312899</v>
+        <v>0.2051398344596804</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2053174380004864</v>
+        <v>0.2068674380004864</v>
       </c>
       <c r="C96">
-        <v>-8363.059927876933</v>
+        <v>-8484.604279147297</v>
       </c>
       <c r="D96">
-        <v>1481.845979424638</v>
+        <v>1467.585733551098</v>
       </c>
       <c r="E96">
-        <v>8131.99536761905</v>
+        <v>8239.279473015875</v>
       </c>
       <c r="F96">
-        <v>10084.70590730157</v>
+        <v>10191.9900126984</v>
       </c>
       <c r="G96">
         <v>239.8</v>
@@ -9165,37 +9165,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M96">
-        <v>2025.008946186156</v>
+        <v>2046.551594549838</v>
       </c>
       <c r="N96">
-        <v>-1609.598946186156</v>
+        <v>-1631.141594549838</v>
       </c>
       <c r="O96">
-        <v>-415.2765281160283</v>
+        <v>-420.8345313938582</v>
       </c>
       <c r="P96">
-        <v>-1194.322418070128</v>
+        <v>-1210.30706315598</v>
       </c>
       <c r="Q96">
-        <v>-1058.022418070128</v>
+        <v>-1074.00706315598</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4425890156873548</v>
+        <v>0.521946818824826</v>
       </c>
       <c r="T96">
-        <v>9.163718607098263</v>
+        <v>10.99646232851792</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.05292607729059755</v>
+        <v>0.05236896068753864</v>
       </c>
       <c r="W96">
-        <v>0.190172443680048</v>
+        <v>0.1902843126939422</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2051398344596804</v>
+        <v>0.2029804677811575</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2068674380004864</v>
+        <v>0.2084174380004864</v>
       </c>
       <c r="C97">
-        <v>-8484.604279147297</v>
+        <v>-8605.876785265315</v>
       </c>
       <c r="D97">
-        <v>1467.585733551098</v>
+        <v>1453.597332829906</v>
       </c>
       <c r="E97">
-        <v>8239.279473015875</v>
+        <v>8346.563578412701</v>
       </c>
       <c r="F97">
-        <v>10191.9900126984</v>
+        <v>10299.27411809522</v>
       </c>
       <c r="G97">
         <v>239.8</v>
@@ -9247,37 +9247,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M97">
-        <v>2046.551594549838</v>
+        <v>2068.094242913521</v>
       </c>
       <c r="N97">
-        <v>-1631.141594549838</v>
+        <v>-1652.684242913521</v>
       </c>
       <c r="O97">
-        <v>-420.8345313938582</v>
+        <v>-426.3925346716884</v>
       </c>
       <c r="P97">
-        <v>-1210.30706315598</v>
+        <v>-1226.291708241833</v>
       </c>
       <c r="Q97">
-        <v>-1074.00706315598</v>
+        <v>-1089.991708241833</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.521946818824826</v>
+        <v>0.6409835235310326</v>
       </c>
       <c r="T97">
-        <v>10.99646232851792</v>
+        <v>13.7455779106474</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.05236896068753864</v>
+        <v>0.05182345068037678</v>
       </c>
       <c r="W97">
-        <v>0.1902843126939422</v>
+        <v>0.1903938511033804</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2029804677811575</v>
+        <v>0.2008660879084371</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2084174380004864</v>
+        <v>0.2441024479358229</v>
       </c>
       <c r="C98">
-        <v>-8605.876785265313</v>
+        <v>-8974.739281670207</v>
       </c>
       <c r="D98">
-        <v>1453.597332829907</v>
+        <v>1192.018941821839</v>
       </c>
       <c r="E98">
-        <v>8346.563578412699</v>
+        <v>8453.847683809525</v>
       </c>
       <c r="F98">
-        <v>10299.27411809522</v>
+        <v>10406.55822349205</v>
       </c>
       <c r="G98">
         <v>239.8</v>
@@ -9329,45 +9329,45 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M98">
-        <v>2068.09424291352</v>
+        <v>2453.866429099424</v>
       </c>
       <c r="N98">
-        <v>-1652.68424291352</v>
+        <v>-2038.456429099424</v>
       </c>
       <c r="O98">
-        <v>-426.3925346716883</v>
+        <v>-525.9217587076515</v>
       </c>
       <c r="P98">
-        <v>-1226.291708241832</v>
+        <v>-1512.534670391773</v>
       </c>
       <c r="Q98">
-        <v>-1089.991708241832</v>
+        <v>-1376.234670391773</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6409835235310309</v>
+        <v>0.8455450292192567</v>
       </c>
       <c r="T98">
-        <v>13.74557791064737</v>
+        <v>18.46986210668029</v>
       </c>
       <c r="U98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05182345068037678</v>
+        <v>0.04367628927518023</v>
       </c>
       <c r="W98">
-        <v>0.1903938511033804</v>
+        <v>0.2255011309889125</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.2008660879084371</v>
+        <v>0.1692879429270551</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2441024479358229</v>
+        <v>0.2460024479358228</v>
       </c>
       <c r="C99">
-        <v>-8974.739281670207</v>
+        <v>-9093.336115821417</v>
       </c>
       <c r="D99">
-        <v>1192.018941821839</v>
+        <v>1180.706213067455</v>
       </c>
       <c r="E99">
-        <v>8453.847683809525</v>
+        <v>8561.131789206351</v>
       </c>
       <c r="F99">
-        <v>10406.55822349205</v>
+        <v>10513.84232888887</v>
       </c>
       <c r="G99">
         <v>239.8</v>
@@ -9411,37 +9411,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M99">
-        <v>2453.866429099424</v>
+        <v>2479.164021151996</v>
       </c>
       <c r="N99">
-        <v>-2038.456429099424</v>
+        <v>-2063.754021151996</v>
       </c>
       <c r="O99">
-        <v>-525.9217587076515</v>
+        <v>-532.448537457215</v>
       </c>
       <c r="P99">
-        <v>-1512.534670391773</v>
+        <v>-1531.305483694781</v>
       </c>
       <c r="Q99">
-        <v>-1376.234670391773</v>
+        <v>-1395.005483694781</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8455450292192567</v>
+        <v>1.245417543828885</v>
       </c>
       <c r="T99">
-        <v>18.46986210668029</v>
+        <v>27.70479316002043</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04367628927518023</v>
+        <v>0.0432306128540049</v>
       </c>
       <c r="W99">
-        <v>0.2255011309889125</v>
+        <v>0.2256062214890256</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1692879429270551</v>
+        <v>0.1675605149380035</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2460024479358228</v>
+        <v>0.2479024479358228</v>
       </c>
       <c r="C100">
-        <v>-9093.336115821417</v>
+        <v>-9211.720244140974</v>
       </c>
       <c r="D100">
-        <v>1180.706213067455</v>
+        <v>1169.606190144722</v>
       </c>
       <c r="E100">
-        <v>8561.131789206351</v>
+        <v>8668.415894603175</v>
       </c>
       <c r="F100">
-        <v>10513.84232888887</v>
+        <v>10621.1264342857</v>
       </c>
       <c r="G100">
         <v>239.8</v>
@@ -9493,37 +9493,37 @@
         <v>415.4099999999999</v>
       </c>
       <c r="M100">
-        <v>2479.164021151996</v>
+        <v>2504.461613204567</v>
       </c>
       <c r="N100">
-        <v>-2063.754021151996</v>
+        <v>-2089.051613204567</v>
       </c>
       <c r="O100">
-        <v>-532.448537457215</v>
+        <v>-538.9753162067784</v>
       </c>
       <c r="P100">
-        <v>-1531.305483694781</v>
+        <v>-1550.076296997789</v>
       </c>
       <c r="Q100">
-        <v>-1395.005483694781</v>
+        <v>-1413.776296997789</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.245417543828885</v>
+        <v>2.44503508765777</v>
       </c>
       <c r="T100">
-        <v>27.70479316002043</v>
+        <v>55.40958632004087</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.0432306128540049</v>
+        <v>0.04279393999689376</v>
       </c>
       <c r="W100">
-        <v>0.2256062214890256</v>
+        <v>0.2257091889487325</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1675605149380035</v>
+        <v>0.1658679844840842</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2479024479358228</v>
-      </c>
-      <c r="C101">
-        <v>-9211.720244140974</v>
-      </c>
-      <c r="D101">
-        <v>1169.606190144722</v>
-      </c>
-      <c r="E101">
-        <v>8668.415894603175</v>
-      </c>
-      <c r="F101">
-        <v>10621.1264342857</v>
-      </c>
-      <c r="G101">
-        <v>239.8</v>
-      </c>
-      <c r="H101">
-        <v>8775.700000000001</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>551.7099999999999</v>
-      </c>
-      <c r="K101">
-        <v>136.3</v>
-      </c>
-      <c r="L101">
-        <v>415.4099999999999</v>
-      </c>
-      <c r="M101">
-        <v>2504.461613204567</v>
-      </c>
-      <c r="N101">
-        <v>-2089.051613204567</v>
-      </c>
-      <c r="O101">
-        <v>-538.9753162067784</v>
-      </c>
-      <c r="P101">
-        <v>-1550.076296997789</v>
-      </c>
-      <c r="Q101">
-        <v>-1413.776296997789</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.44503508765777</v>
-      </c>
-      <c r="T101">
-        <v>55.40958632004087</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04279393999689376</v>
-      </c>
-      <c r="W101">
-        <v>0.2257091889487325</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1658679844840842</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
